--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2646,6 +2646,2206 @@
         </is>
       </c>
       <c r="D101" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>B0CNVTCK51</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>€9.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>B0CNVTCK51</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>€9.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>B0BPNT6XYY</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>B0BPNT6XYY</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>B0F93BDHHF</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>€22.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>B0F93BDHHF</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>€22.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>B0DJS84VNY</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>B0DJS84VNY</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>B0DWXHV7L5</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>B0DWXHV7L5</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>B0F6MRMCCQ</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>B0F6MRMCCQ</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>B0FXFX6W31</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>#14</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>B0FXFX6W31</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>#15</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>B0GHNJ6ZY3</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>€9.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>#16</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>B0GHNJ6ZY3</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>€9.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>#17</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>B0DSZLRYTB</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>#18</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>B0DSZLRYTB</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>#19</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>B0DLKLY2RS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>#20</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>B0DLKLY2RS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>#21</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>B0GCHZ4RP5</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>#22</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>B0GCHZ4RP5</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>#23</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>B0DJTDNSQN</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>#24</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>B0DJTDNSQN</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>#25</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>B0C2CM7QWR</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>€14.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>#26</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>B0C2CM7QWR</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>€14.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>#27</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>B0DM4WJ7XH</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>#28</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>B0DM4WJ7XH</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>#29</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>B0DSW4V65Z</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>#30</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>B0DSW4V65Z</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>#31</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>B0DSZXH6BG</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>#32</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>B0DSZXH6BG</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>#33</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>B0DWSTJ4HS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>€17.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>#34</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>B0DWSTJ4HS</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>€17.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>#35</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>B0DK8SYX8F</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>€9.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>#36</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>B0DK8SYX8F</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>€9.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>#37</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>B0DK9528FW</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>€9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>B0DK9528FW</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>€9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>#39</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>B0CFV96666</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>#40</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>B0CFV96666</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>#41</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>B0F9YKRBCJ</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>#42</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>B0F9YKRBCJ</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>#43</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>B0D7YT3ZMX</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>#44</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>B0D7YT3ZMX</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>#45</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>B0CYGJ2RNV</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>€9.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>#46</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>B0CYGJ2RNV</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>€9.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>#47</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>B0F2MV5NGP</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>#48</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>B0F2MV5NGP</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>#49</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>B0FXG8CR1V</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>#50</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>B0FXG8CR1V</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>#51</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>B0BTH76GS7</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>€10.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>#52</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>B0BTH76GS7</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>€10.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>#53</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>B0FFYWVP45</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>€11.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>#54</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>B0FFYWVP45</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>€11.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>#55</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>B0G6C44RPY</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>#56</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>B0G6C44RPY</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>#57</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>B0F6LP1M79</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>#58</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>B0F6LP1M79</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>#59</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>B0GDJSFDL4</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>#60</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>B0GDJSFDL4</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>#61</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>B0F6CNSRNC</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>#62</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>B0F6CNSRNC</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>#63</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>B0FFSF5NHR</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>#64</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>B0FFSF5NHR</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>#65</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>B0FXX82RGG</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>€17.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>#66</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>B0FXX82RGG</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>€17.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>#67</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>B0GJN22NJV</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>#68</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>B0GJN22NJV</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>#69</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>B0FVL3BV29</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>#70</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>B0FVL3BV29</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>#71</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>B0DFPRVGN7</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>€5.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>#72</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>B0DFPRVGN7</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>€5.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>#73</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>B0FDKND69M</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>€13.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>#74</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>B0FDKND69M</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>€13.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>#75</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>B0DM5YLYHB</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>#76</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>B0DM5YLYHB</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>#77</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>B0D5JRJCVX</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>€12.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>#78</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>B0D5JRJCVX</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>€12.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>#79</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>B0GF6SBD6J</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>#80</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>B0GF6SBD6J</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>#81</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>B0G3WZMGZJ</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>€6.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>#82</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>B0G3WZMGZJ</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>€6.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>#83</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>B0DDSPNKNT</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>€12.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>#84</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>B0DDSPNKNT</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>€12.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>#85</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>B0FJY96R5S</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>#86</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>B0FJY96R5S</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>#87</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>B0DJTD19WX</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>#88</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>B0DJTD19WX</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>#89</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>B0FPF2PBNM</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>#90</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>B0FPF2PBNM</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>#91</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>B0D8KHVX7S</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>€10.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>#92</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>B0D8KHVX7S</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>€10.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>#93</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>B0CCND87VQ</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>€8.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>#94</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>B0CCND87VQ</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>€8.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>#95</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>B0F2GHWNK3</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>#96</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>B0F2GHWNK3</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>#97</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>B0DXZZKPQ3</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>#98</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>B0DXZZKPQ3</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>#99</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>B0F5B537XQ</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>#100</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>B0F5B537XQ</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
         <is>
           <t>€10.99</t>
         </is>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4846,6 +4846,2206 @@
         </is>
       </c>
       <c r="D201" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>B0CNVTCK51</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>€9.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>B0CNVTCK51</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>€9.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>B0BPNT6XYY</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>B0BPNT6XYY</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>B0F93BDHHF</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>€22.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>B0F93BDHHF</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>€22.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>B0DJS84VNY</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>B0DJS84VNY</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>B0DWXHV7L5</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>B0DWXHV7L5</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>B0F6MRMCCQ</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>B0F6MRMCCQ</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>B0FXFX6W31</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>#14</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>B0FXFX6W31</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>#15</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>B0GHNJ6ZY3</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>€9.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>#16</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>B0GHNJ6ZY3</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>€9.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>#17</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>B0DSZLRYTB</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>#18</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>B0DSZLRYTB</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>#19</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>B0DLKLY2RS</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>#20</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>B0DLKLY2RS</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>#21</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>B0GCHZ4RP5</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>#22</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>B0GCHZ4RP5</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>#23</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>B0DJTDNSQN</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>#24</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>B0DJTDNSQN</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>#25</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>B0C2CM7QWR</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>€14.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>#26</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>B0C2CM7QWR</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>€14.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>#27</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>B0DM4WJ7XH</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>#28</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>B0DM4WJ7XH</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>#29</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>B0DSW4V65Z</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>#30</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>B0DSW4V65Z</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>#31</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>B0DSZXH6BG</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>#32</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>B0DSZXH6BG</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>#33</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>B0DWSTJ4HS</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>€17.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>#34</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>B0DWSTJ4HS</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>€17.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>#35</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>B0DK8SYX8F</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>€9.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>#36</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>B0DK8SYX8F</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>€9.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>#37</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>B0DK9528FW</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>€9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>B0DK9528FW</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>€9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>#39</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>B0CFV96666</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>#40</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>B0CFV96666</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>#41</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>B0F9YKRBCJ</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>#42</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>B0F9YKRBCJ</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>#43</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>B0D7YT3ZMX</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>#44</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>B0D7YT3ZMX</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>#45</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>B0CYGJ2RNV</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>€9.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>#46</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>B0CYGJ2RNV</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>€9.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>#47</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>B0F2MV5NGP</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>#48</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>B0F2MV5NGP</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>#49</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>B0FXG8CR1V</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>#50</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>B0FXG8CR1V</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>#51</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>B0BTH76GS7</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>€10.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>#52</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>B0BTH76GS7</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>€10.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>#53</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>B0FFYWVP45</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>€11.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>#54</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>B0FFYWVP45</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>€11.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>#55</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>B0G6C44RPY</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>#56</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>B0G6C44RPY</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>#57</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>B0F6LP1M79</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>#58</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>B0F6LP1M79</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>#59</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>B0GDJSFDL4</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>#60</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>B0GDJSFDL4</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>#61</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>B0F6CNSRNC</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>#62</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>B0F6CNSRNC</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>#63</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>B0FFSF5NHR</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>#64</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>B0FFSF5NHR</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>#65</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>B0FXX82RGG</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>€17.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>#66</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>B0FXX82RGG</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>€17.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>#67</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>B0GJN22NJV</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>#68</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>B0GJN22NJV</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>#69</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>B0FVL3BV29</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>#70</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>B0FVL3BV29</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>#71</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>B0DFPRVGN7</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>€5.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>#72</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>B0DFPRVGN7</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>€5.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>#73</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>B0FDKND69M</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>€13.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>#74</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>B0FDKND69M</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>€13.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>#75</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>B0DM5YLYHB</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>#76</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>B0DM5YLYHB</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>#77</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>B0D5JRJCVX</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>€12.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>#78</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>B0D5JRJCVX</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>€12.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>#79</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>B0GF6SBD6J</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>#80</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>B0GF6SBD6J</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>#81</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>B0G3WZMGZJ</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>€6.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>#82</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>B0G3WZMGZJ</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>€6.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>#83</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>B0DDSPNKNT</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>€12.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>#84</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>B0DDSPNKNT</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>€12.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>#85</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>B0FJY96R5S</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>#86</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>B0FJY96R5S</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>#87</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>B0DJTD19WX</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>#88</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>B0DJTD19WX</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>#89</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>B0FPF2PBNM</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>#90</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>B0FPF2PBNM</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>#91</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>B0D8KHVX7S</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>€10.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>#92</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>B0D8KHVX7S</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>€10.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>#93</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>B0CCND87VQ</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>€8.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>#94</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>B0CCND87VQ</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>€8.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>#95</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>B0F2GHWNK3</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>#96</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>B0F2GHWNK3</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>#97</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>B0DXZZKPQ3</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>#98</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>B0DXZZKPQ3</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>#99</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>B0F5B537XQ</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>#100</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>B0F5B537XQ</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
         <is>
           <t>€10.99</t>
         </is>
@@ -4862,7 +7062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4896,6 +7096,56 @@
           <t>Date_Detection</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Titre_Complet</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Nb_Avis</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Bullet_Points</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Nombre_Images</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Caracteristiques</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>BSR_Categories</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Declinaisons</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Nb_Declinaisons</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Date_Analyse</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4910,12 +7160,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description textuelle</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4924,6 +7174,52 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -4942,12 +7238,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description textuelle</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4956,6 +7252,52 @@
         </is>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -4974,12 +7316,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description textuelle</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4988,6 +7330,52 @@
         </is>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5006,12 +7394,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description textuelle</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5020,6 +7408,52 @@
         </is>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5038,12 +7472,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description textuelle</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5052,6 +7486,52 @@
         </is>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5070,12 +7550,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description textuelle</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5084,6 +7564,52 @@
         </is>
       </c>
       <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5102,12 +7628,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Visit the HWeggo Store</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description textuelle</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5116,6 +7642,52 @@
         </is>
       </c>
       <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[2 in 1] Waterproof Case for Apple Watch Series Ultra 3/Ultra 2/Ultra 49mm Accessories, 360° Front and Back, iWatch PC Screen Protector with Tempered Glass for Women and Men, 49mm Black</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.3 out of 5 stars</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>(2,040)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>【COMPATIBILITY】Tensea iWatch screen protector with back cover is designed to fit Apple Watch Ultra 3 49mm, Apple Watch Ultra 2 49mm and Apple Watch Ultra 49mm. The bumper cover built into the screen protector provides a perfect fit. | 【Daily Water Resistance】 Apple Watch Ultra 3/Ultra 2/Ultra 49mm has a built-in seal that effectively prevents water from entering the screen. Its exceptional water resistance for everyday use makes it possible to use it with confidence during activities such as showering, hand washing, sweating or showering. [Note: Not suitable for deep water environments such as diving or swimming.] | 【360°Protection】This protective case, compatible with the surface of iWatch Ultra 3/Ultra 2/Ultra 49mm, provides full protection to the front and back of your watch, effectively resisting dust, dirt, scratches and damage. The 9H tempered glass screen protector preserves touch sensitivity, while the sweat-resistant case design allows for easy installation without having to remove the band. | 【Upgraded Materials】 Scratch-resistant and impact-resistant tempered glass has a hardness of 9H. Shock absorbing polycarbonate provides superior rigidity, improved resilience and better protection compared to conventional TPU. Glass construction prevents fogging caused by temperature fluctuations. | 【Easy Installation】The product page includes installation video and the package contains installation instructions. A removal tool is provided to allow the watch case to be removed without damaging it.</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5134,20 +7706,62 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
+          <t>Brand: TUTUO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TUTUO For Garmin Forerunner 165/165 Music Case, [2 Pieces] Full Coverage Protective Case with Screen Protector, Anti-Scratch Shockproof TPU Case – Transparent+Black</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4.4 out of 5 stars</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>(61)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Compatible Model: Compatible with Garmin Forerunner 165 / 165 Music. Precise design will fit your watch perfectly. (Note: Please check your watch model number before purchasing) | Full protection: The protective case for Garmin Forerunner 165 / 165 Music offers full screen protection from four sides to the corners. Slightly higher edges protect the surface of your watch and protect it from scratches, bumps and accidental drops. | Effective protective TPU material: made of high-quality and scratch-resistant TPU material. Soft and lightweight, very comfortable to wear, leaves no air bubbles between the case and the screen, giving you an original viewing experience and touch experience. | Easy to install: no tools required. You don't need to remove the case, just align the holes with the watch buttons and put the case in place. Precise cutouts for quick access to screen, button and sensor. The case does not need to be removed when charging. | Fashion and Light: Soft and thin TPU materials make it easy to put on and take off your watch. Slim and lightweight, never strain your wrist from work to exercise. Give you a better user experience.</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'GM 165', 'Compatible Phone Models': 'Garmin Forerunner 165, Garmin Forerunner 165 Music', 'Special Features': 'Effective protective TPU material, full protection', 'Clarity': '10', 'Compatible Wearable Computer Models': 'Garmin Forerunner 165', 'Item Dimensions L x W': '10L x 6W centimetres', 'Unit Count': '2.0 unité', 'Number of Items': '2', 'Material': 'Silicone', 'Brand Name': 'TUTUO', 'Model Number': 'GM 165-HS+TM', 'Model Name': 'GM 165-HS+TM', 'Colour': 'Transparent/Green', 'Manufacturer': 'TUTUO', 'Part Number': 'GM 165-HS+TM', 'Best Sellers Rank': '4,130 in Electronics (See Top 100 in Electronics) 8 in Smartwatch Cases', 'ASIN': 'B0GHNJ6ZY3', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (61)   \n\n\n 4.4 out of 5 stars'}</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5166,12 +7780,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Brand: Kamita</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description textuelle</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5180,6 +7794,52 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[3 Pieces] Kamita Case Compatible with Garmin Vivoactive 5, Complete Protective Case with Tempered Glass Screen Protector, Shockproof Hard PC Bumper Case for Garmin Vivo Active 5 (Clear+Pink+White)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.2 out of 5 stars</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>(192)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>COMPATIBILITY: This specially designed Kamita protective case is compatible with Garmin Vivoactive 5, which can provide full protection for your watch. The screen protectors and protective case fit your watch perfectly. NOTE: This case does not fit other watch models. Please check the model of your watch before purchasing. | New material: This case compatible with Garmin Vivoactive 5 is made of hard and durable PC, which is more resistant to wear and does not lose its colors. The smooth surface ensures smooth gliding and tactile sensitivity, which gives you a better touch feeling. | Total protection: our Garmin Vivo Active 5 hard PC cases can cover all sides of your watch, ensuring total protection for your watch. Shockproof and scratch resistant design protects the watch from bumps and scratches. | Precise cutouts and easy installation: Our watch cover has a precise button cut-out that allows it to snap into place quickly and fit your watch precisely. Allows easy access to all buttons, sound holes, sensors and smartwatch functions. What's more, the snap-on design is easy to install and remove without any tools. It is also not necessary to remove the case to charge. | Package includes: The package includes 3 pieces of covers for Garmin Vivo Active 5. Humanized ergonomic house, air cushion technology to protect all areas. Suitable for men, women, girls, boys and any occasion.</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatches', 'Form Factor': 'Case', 'Product Features': 'Shock and scratch resistant', 'Compatible Phone Models': 'Garmin Vivoactive 5', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Transparent+Pink+White', 'Shell Type': 'Hard', 'Enclosure Material': 'Polycarbonate', 'Brand Name': 'Kamita', 'Unit Count': '3.0 count', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '4,168 in Electronics (See Top 100 in Electronics) 9 in Smartwatch Cases', 'ASIN': 'B0DSZLRYTB', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (192)   \n\n\n 4.2 out of 5 stars', 'Item Dimensions': '8 x 1 x 1.3 centimetres'}</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5198,12 +7858,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Brand: Amizee</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description textuelle</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5212,6 +7872,52 @@
         </is>
       </c>
       <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Amizee 2 in 1 Case Compatible with Apple Watch Series 11/10 46mm, Hard Metal Material Full Protection Rugged Anti-Scratch Case for iWatch 46mm, Black</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4.1 out of 5 stars</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>(1,683)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>【Compatible Models】Amizee cover only compatible with Apple Watch Series 11 (2025)/Series 10 46mm Cover. Note: Not suitable for other models and other types for smartwatch. Please confirm your watch size before placing an order. | 【Ultra 3/2/1 Second Change】Simple and tool-free installation transforms the appearance of your watch in seconds, allowing you to enjoy the Ultra 3/2/1 wearing experience, providing a stylish yet functional design and giving you a personal experience. The right button of the case has an updated built-in watch crown cover. (Note: crown does not work for ECG) | 【High quality metal casing】Made of high quality shockproof metal aluminum. Brighten up your Apple Watch and provide full protection without sacrificing beauty, and has long lasting protection against shocks. The snap-on design of the case is easy to install and remove. Charge directly, without removing the case. | 【Metal Bezel Protection】Raised edges around the screen for extra protection of the Apple Watch screen from scratches, bumps and accidental drops. Featuring an aluminum alloy frame, you will feel sturdy from the inside. (Note: does not include the built-in screen protector) | 【What you get】1 x black apple watch case 46 mm. If you have any defects or quality problems of our Apple Watch cases, please feel free to contact us, our customer service will reply you within 24 hours.</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Apple Watch Series 10 46mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '46 Millimetres', 'Product Features': 'Heavy Duty Protection', 'Compatible Phone Models': 'Apple Watch Series 11(2025)/Series 10 46mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black', 'Pattern': 'Sports', 'Theme': 'Sport', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Unit Count': '1.0 count', 'Manufacturer Part Number': 'BENQ3-CASE', 'Model Number': 'BENQ3-CASE', 'Manufacturer': 'Amizee', 'Age Range Description': 'Adult', 'Best Sellers Rank': '4,237 in Electronics (See Top 100 in Electronics) 10 in Smartwatch Cases', 'ASIN': 'B0DLKLY2RS', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (1,683)   \n\n\n 4.1 out of 5 stars', 'Item Dimensions': '11 x 45 x 50 millimetres'}</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5230,12 +7936,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Brand: Amizee</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Amizee 2 in 1 Metal Case Compatible with Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47mm, Ultra Thin Hard PC Bumper Anti-Scratch Protective Case for Galaxy Watch 7/8 Ultra, Blue/White</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5244,6 +7950,52 @@
         </is>
       </c>
       <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Amizee 2 in 1 Metal Case Compatible with Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47mm, Ultra Thin Hard PC Bumper Anti-Scratch Protective Case for Galaxy Watch 7/8 Ultra, Blue/White</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.5 out of 5 stars</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>(907)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Compatible models: Amizee cover only compatible with Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47 mm. Note: Not suitable for other models and other types for smartwatch. Please confirm your watch size before placing an order. | 【High Quality Metal Casing】Made of high quality impact-resistant aluminum, metal and PC material. Brighten up your Samsung Galaxy Watch and ensure full protection without sacrificing beauty, and features long lasting protection against bumps. | 【Metal Bezel Protection】Raised edges around the screen provide extra protection for the Samsung Galaxy Watch screen from scratches, bumps and accidental drops. Featuring an aluminum alloy frame, you will feel sturdy from the inside. (Note: Does not include a built-in screen protector.) | 【Easy to snap on】 The snap-on design of the case is easy to install and remove. Simply press the side of the back cover case into the alignment of the crown hole. No tools, without removing the Galaxy Watch. Charge directly, without removing the case. Snap button design on the back prevents the watch from falling off. | 【What you get】1 x Blue/White Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47 mm cover. If you have any defects or quality problems of our Apple Watch cases, please feel free to contact us, our customer service will reply you within 24 hours.</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '47 Millimetres', 'Product Features': 'Kickstand, Protection for demanding use, Wireless', 'Compatible Phone Models': 'Samsung Galaxy Watch Ultra/Ultra 2(2025) 47mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Blue / white', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Manufacturer Part Number': 'GALAXYCASE-BK', 'Model Number': 'SGUltra-CASE-BUWhite', 'Manufacturer': 'Amizee', 'Best Sellers Rank': '4,485 in Electronics (See Top 100 in Electronics) 11 in Smartwatch Cases', 'ASIN': 'B0GCHZ4RP5', 'Customer Reviews': '4.5  4.5 out of 5 stars   \n    (907)   \n\n\n 4.5 out of 5 stars', 'Item Dimensions': '48 x 46 x 16 millimetres', 'Item Weight': '0.47 Ounces'}</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5262,12 +8014,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Visit the ivoler Store</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Fulfills Your Expectations Choose iVoler case, it does not make your watch look huge and bulky, but it is very thin and the case is matte, which makes your watch very elegant and gives it a natural look, so fashion and luxury. Perfect fit Precise hole cutouts make it easy to access all buttons. 360 Degree Full Protection Our case covers the full front and curved edges of the watch, provides full protection of your watch against dust, fingerprints, scratches, drop or dent to the ground. Sensitive Touch &amp; HD Clear 99% high transparency provides clear image quality and maintains the original touch sensitivity without affecting the use of touch. Easy to install and remove Ultra-soft material makes this case very flexible, easy to install and remove. This does not affect the use of load and strap after installation. After-sales Service We pay great attention to product quality problems and customer experienceIf you have any questions about our products, please feel free to contact us, we will reply you promptly within 24 hours. Note: These covers cannot support swimming as water will be trapped under the covers. During fitness or other sports, it may cause water mist between the watch screen and the screen protector. Please use a dry cloth to clean if water, sweat or moisture gets under the case, as it may affect the responsiveness to touch.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5276,6 +8028,52 @@
         </is>
       </c>
       <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ivoler 3 Pieces Case with Screen Protector for Huawei Watch GT 5 46mm, Full Protective Soft TPU Thin Shockproof Anti-Scratch Cover Case (2 Transparent + 1 Black)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4.3 out of 5 stars</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>(361)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>[Applicable Model]---- Compatible with Huawei Watch GT 5 46mm (Not for Huawei Watch GT 5 41mm). This case is designed with precise cutouts for functional buttons, speaker hole, charging hole, etc.(The package only contains cases, watch and watch band are not included!) | [Full Protection] --- Our case covers the full front and curved edges of the watch, provides complete protection of your watch against dust, fingerprints, scratches, drops or bumps to the ground. | [Sensitive Touch and High Transparency]---- Made of premium TPU material, smooth, transparent and without influencing touch sensitivity. Gives you original touch sensitivity and high touch responsiveness. Hydrophobic and oleophobic screen coating can easily separate oil, fingerprints and other stains, make the screen easy to clean, prevent your watch screens from looking shabby and dull. | [Ultra Slim and Easy to Install] ---- Ultra thin and lightweight, never be a burden on your wrist from your work to your workout. Easy to wear and remove and designed to be compatible with the charger, you don't need to remove the protective case when charging. | [What you get] --- 3 x iVoler cases with built-in screen protector (2 transparent + 1 black). [Warm Tip]: Using this product in the gym or during sports activities may cause moisture (sweating) to build up between this product and the monitor screen. Use dry cloth to keep it dry if you have water, if you have any questions or product problems, please contact us, we will do the best service for you.</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'huawei watch gt 5 46mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'huawei watch gt 5 46mm', 'Special Features': 'Rounded Edge, Shockproof', 'Screen Size': '46 Millimetres', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Compatible Wearable Computer Models': 'Huawei WATCH GT, SUUNTO 5', 'Unit Count': '3.0 count', 'Number of Items': '3', 'Brand Name': 'ivoler', 'Model Name': 'iVoler Huawei Watch GT 5 46mm Screen Protector', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00039', 'Best Sellers Rank': '3,967 in Electronics (See Top 100 in Electronics) 12 in Smartwatch Cases', 'ASIN': 'B0DJTDNSQN', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (361)   \n\n\n 4.3 out of 5 stars', 'Material': 'Silicone'}</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5294,12 +8092,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Brand: Amizee</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description textuelle</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5308,6 +8106,52 @@
         </is>
       </c>
       <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Amizee 2 in 1 Case [2 Pieces] Compatible with Apple Watch SE 3/2/1 Series 6/5/4 40mm with Screen Protector, Full Coverage Anti-Scratch Case Cover for iWatch 40mm (Black)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4.1 out of 5 stars</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>(3,036)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>【Compatible Models】Designed for Apple Watch SE 3/2/1 Series 6/5/4 40mm. NOTE: Not suitable for other models and other types of smartwatch. Please confirm your watch size before placing an order. | 【Full Body Protection】Made of high quality hard PC material, with built-in screen protector. 2 in 1 design provides robust 360 degree protection. Full body protection keeps your Apple Watch 40mm from scratches and drops. | High sensitivity touch: The high-transparency tempered glass screen protector provides original vision and touch experience; Ultra-thin, three-dimensional right-angle edge, the design is slimmer. | 【Precise Fit】Sensitive button covers allow responsive pressing; Easy access to Apple Watch button and functions with precise cutouts; Easy to install, charge directly, without removing the case. | 【WHAT YOU GET】2 x Black Apple Watch Case 40 mm; We offer a one-year warranty, please feel free to contact us for any problem, a satisfactory solution is promised forever.</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Apple Watch Series 6/5/4/SE 40mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'Apple Watch', 'Special Features': 'Robust protection, Scratch Resistant, Shockproof, screen protector', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Waterproof', 'Screen Size': '44 Millimetres', 'Screen Surface Description': 'Matte', 'Clarity': '0.99', 'Compatible Wearable Computer Models': 'Apple Watch SE 40mm', 'Item Dimensions L x W': '43L x 38W millimetres', 'Unit Count': '1.0 unité', 'Number of Items': '2', 'Brand Name': 'Amizee', 'Model Number': 'APPLECASE-ZB', 'Model Name': 'CAZB-40-BLC', 'Colour': 'Black / Black', 'Manufacturer': 'Amizee', 'Part Number': 'CAZB-40-BLC', 'Item Weight': '0.18 Ounces', 'Included Components': 'Case for Apple Watch 40mm', 'Best Sellers Rank': '3,327 in Electronics (See Top 100 in Electronics) 13 in Smartwatch Cases 92 in Smartwatch Screen Protectors &amp; Foils', 'ASIN': 'B0C2CM7QWR', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (3,036)   \n\n\n 4.1 out of 5 stars', 'Material': 'Polycarbonate, Tempered Glass'}</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5326,12 +8170,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Brand: Bigqin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Features: 【PC + High Quality Tempered Film】 The case does not affect touch sensitivity. Provide original touch sensitivity. 【Precise Cutouts】 Precise cutouts for all connections, speakers and buttons, easy access to all functions and controls. 【Full Protection】 The edge and screen protector are integrally formed. It protects the watch from scratches, collisions or other damage. Warm Tips: The screen protector case is not waterproof, please take it off while swimming or bathing. Moisture can be trapped in case you are exercising, please just use the microfiber cloth to wipe it off. Package contents: 4 x watch case with screen protector compatible with Xiaomi Redmi Watch 5 Active. Colour: Clear, Black, Blue, Pink</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5340,6 +8184,52 @@
         </is>
       </c>
       <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4-Piece Case Compatible with Xiaomi Redmi Watch 5 Active, Hard PC Case with Screen Protector, HD Case with Tempered Glass – Transparent, Black, Pink, Blue</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4.2 out of 5 stars</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>(540)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1. Compatible models: Only compatible with Xiaomi Redmi Watch 5 Active, please confirm your watch model before purchasing. 4 colours per pack: transparent, black, pink, blue. | 2. Full protection: It protects the watch screen and sides from scratches, scrapes, chips, collisions or other damage. | 3. Material: durable PC case with screen protector. No influence on touch sensitivity, sensor functions work well with watch case. | 4. Easy to install: its snap-on design to avoid peeling off. Precise hole cutouts make it easy to access all buttons or buttons, slim and lightweight, no need to remove the watch case when charging. | 5. Tips: Recommended for removing the case when swimming or bathing. Moisture can be trapped in case when you exercise, please use the microfiber cloth to wipe it.</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Xiaomi Redmi Watch 5 Active', 'Special Features': 'High quality tempered glass', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Not Water Resistant', 'Screen Surface Description': 'Glossy', 'Clarity': '10', 'Unit Count': '4.0 count', 'Number of Items': '4', 'Material': 'Polycarbonate', 'Brand Name': 'Bigqin', 'Model Number': '13XMRMW5A-4PC', 'Model Name': 'Xiaomi Redmi Watch 5 Active Screen Protector 4-Pack', 'Customer Package Type': 'FFP Packaging', 'Colour': 'Redmi Watch 5 Active', 'Manufacturer': 'Bigqin', 'Part Number': 'B02', 'Included Components': 'Watch', 'Best Sellers Rank': '4,821 in Electronics (See Top 100 in Electronics) 14 in Smartwatch Cases', 'ASIN': 'B0DM4WJ7XH', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (540)   \n\n\n 4.2 out of 5 stars'}</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5358,12 +8248,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Visit the ivoler Store</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Fulfills Your Expectations Choose iVoler case, it does not make your watch look huge and bulky, but it is very thin and the case is matte, which makes your watch very elegant and gives it a natural look, so fashion and luxury. Perfect fit Precise hole cutouts make it easy to access all buttons. 360 Degree Full Protection Our case covers the full front and curved edges of the watch, provides full protection of your watch against dust, fingerprints, scratches, drop or dent to the ground. Sensitive Touch &amp; HD Clear 99% high transparency provides clear image quality and maintains the original touch sensitivity without affecting the use of touch. Easy to install and remove Ultra-soft material makes this case very flexible, easy to install and remove. This does not affect the use of load and strap after installation. After-sales Service We pay great attention to product quality problems and customer experienceIf you have any questions about our products, please feel free to contact us, we will reply you promptly within 24 hours. Note: These covers cannot support swimming as water will be trapped under the covers. During fitness or other sports, it may cause water mist between the watch screen and the screen protector. Please use a dry cloth to clean if water, sweat or moisture gets under the case, as it may affect the responsiveness to touch.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5372,6 +8262,52 @@
         </is>
       </c>
       <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ivoler 3 Pieces Case with Screen Protector for Amazfit Active 2 (Round Edition), Full Protective Soft TPU Slim Shockproof Anti-Scratch Cover (2 Transparent + 1 Black)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4.3 out of 5 stars</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>(90)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>[Applicable Model]---- Compatible with Amazfit Active 2 (Round Edition) (Not for Amazfit Active 2 Square Edition). This case is designed with precise cutouts for functional buttons, speaker hole, charging hole, etc.(The package only contains cases, watch and watch band are not included!) | [Full Protection] --- Our case covers the full front and curved edges of the watch, provides complete protection of your watch against dust, fingerprints, scratches, drops or bumps to the ground. | [Sensitive Touch and High Transparency]---- Made of premium TPU material, smooth, transparent and without influencing touch sensitivity. Gives you original touch sensitivity and high touch responsiveness. Hydrophobic and oleophobic screen coating can easily separate oil, fingerprints and other stains, make the screen easy to clean, prevent your watch screens from looking shabby and dull. | [Ultra Slim and Easy to Install] ---- Ultra thin and lightweight, never be a burden on your wrist from your work to your workout. Easy to wear and remove and designed to be compatible with the charger, you don't need to remove the protective case when charging. | [What you get] --- 3 x iVoler cases with built-in screen protector (2 transparent + 1 black). [Warm Tip]: Using this product in the gym or during sports activities may cause moisture (sweating) to build up between this product and the monitor screen. Use dry cloth to keep it dry if you have water, if you have any questions or product problems, please contact us, we will do the best service for you.</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active 2 (Round Edition)', 'Special Features': 'Rounded Edge, Shockproof', 'Finish Type': 'Glossy', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Item Dimensions L x W': '7.2L x 8.2W centimetres', 'Unit Count': '1.0 unité', 'Number of Items': '3', 'Material': 'Silicone', 'Brand Name': 'ivoler', 'Model Name': 'Amazfit Active 2 (Round Edition) Screen Protector', 'Colour': '2 Transparent + 1 Black', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00073', 'Product Warranty': '1', 'Included Components': 'Case', 'Best Sellers Rank': '4,873 in Electronics (See Top 100 in Electronics) 15 in Smartwatch Cases', 'ASIN': 'B0DSW4V65Z', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (90)   \n\n\n 4.3 out of 5 stars'}</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
@@ -5408,6 +8344,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5440,6 +8386,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5472,6 +8428,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5504,6 +8470,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5536,6 +8512,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5568,6 +8554,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5600,6 +8596,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5632,6 +8638,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5664,6 +8680,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5696,6 +8722,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5728,6 +8764,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5760,6 +8806,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5792,6 +8848,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5824,6 +8890,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5856,6 +8932,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5888,6 +8974,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5920,6 +9016,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5952,6 +9058,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5984,6 +9100,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6016,6 +9142,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6048,6 +9184,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6080,6 +9226,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6112,6 +9268,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6144,6 +9310,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6176,6 +9352,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6208,6 +9394,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6240,6 +9436,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6272,6 +9478,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6304,6 +9520,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6336,6 +9562,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6368,6 +9604,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6400,6 +9646,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6432,6 +9688,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6464,6 +9730,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6496,6 +9772,16 @@
           <t>2026-05-17</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -7062,7 +7062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7098,52 +7098,72 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Titre_Complet</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Nb_Avis</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Nb_Avis</t>
+          <t>Bullet_Points</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Bullet_Points</t>
+          <t>Nombre_Images</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Nombre_Images</t>
+          <t>Caracteristiques</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Caracteristiques</t>
+          <t>BSR_Categories</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>BSR_Categories</t>
+          <t>Declinaisons</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Declinaisons</t>
+          <t>Nb_Declinaisons</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Nb_Declinaisons</t>
+          <t>Date_Analyse</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Date_Analyse</t>
+          <t>Bullet_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Bullet_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Bullet_3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Bullet_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Bullet_5</t>
         </is>
       </c>
     </row>
@@ -7180,50 +7200,50 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Aucune caractéristique trouvée</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7258,50 +7278,50 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Aucune caractéristique trouvée</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7336,50 +7356,50 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Aucune caractéristique trouvée</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7414,50 +7434,50 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Aucune caractéristique trouvée</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="N5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7492,50 +7512,50 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Aucune caractéristique trouvée</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="N6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7570,50 +7590,50 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Aucun</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Aucune caractéristique trouvée</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7648,50 +7668,50 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[2 in 1] Waterproof Case for Apple Watch Series Ultra 3/Ultra 2/Ultra 49mm Accessories, 360° Front and Back, iWatch PC Screen Protector with Tempered Glass for Women and Men, 49mm Black</t>
+          <t>4.3 out of 5 stars</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.3 out of 5 stars</t>
+          <t>(2,040)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>(2,040)</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
           <t>【COMPATIBILITY】Tensea iWatch screen protector with back cover is designed to fit Apple Watch Ultra 3 49mm, Apple Watch Ultra 2 49mm and Apple Watch Ultra 49mm. The bumper cover built into the screen protector provides a perfect fit. | 【Daily Water Resistance】 Apple Watch Ultra 3/Ultra 2/Ultra 49mm has a built-in seal that effectively prevents water from entering the screen. Its exceptional water resistance for everyday use makes it possible to use it with confidence during activities such as showering, hand washing, sweating or showering. [Note: Not suitable for deep water environments such as diving or swimming.] | 【360°Protection】This protective case, compatible with the surface of iWatch Ultra 3/Ultra 2/Ultra 49mm, provides full protection to the front and back of your watch, effectively resisting dust, dirt, scratches and damage. The 9H tempered glass screen protector preserves touch sensitivity, while the sweat-resistant case design allows for easy installation without having to remove the band. | 【Upgraded Materials】 Scratch-resistant and impact-resistant tempered glass has a hardness of 9H. Shock absorbing polycarbonate provides superior rigidity, improved resilience and better protection compared to conventional TPU. Glass construction prevents fogging caused by temperature fluctuations. | 【Easy Installation】The product page includes installation video and the package contains installation instructions. A removal tool is provided to allow the watch case to be removed without damaging it.</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Aucune caractéristique trouvée</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="N8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7722,50 +7742,50 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TUTUO For Garmin Forerunner 165/165 Music Case, [2 Pieces] Full Coverage Protective Case with Screen Protector, Anti-Scratch Shockproof TPU Case – Transparent+Black</t>
+          <t>4.4 out of 5 stars</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.4 out of 5 stars</t>
+          <t>(61)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>(61)</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
           <t>Compatible Model: Compatible with Garmin Forerunner 165 / 165 Music. Precise design will fit your watch perfectly. (Note: Please check your watch model number before purchasing) | Full protection: The protective case for Garmin Forerunner 165 / 165 Music offers full screen protection from four sides to the corners. Slightly higher edges protect the surface of your watch and protect it from scratches, bumps and accidental drops. | Effective protective TPU material: made of high-quality and scratch-resistant TPU material. Soft and lightweight, very comfortable to wear, leaves no air bubbles between the case and the screen, giving you an original viewing experience and touch experience. | Easy to install: no tools required. You don't need to remove the case, just align the holes with the watch buttons and put the case in place. Precise cutouts for quick access to screen, button and sensor. The case does not need to be removed when charging. | Fashion and Light: Soft and thin TPU materials make it easy to put on and take off your watch. Slim and lightweight, never strain your wrist from work to exercise. Give you a better user experience.</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="J9" t="n">
         <v>7</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'GM 165', 'Compatible Phone Models': 'Garmin Forerunner 165, Garmin Forerunner 165 Music', 'Special Features': 'Effective protective TPU material, full protection', 'Clarity': '10', 'Compatible Wearable Computer Models': 'Garmin Forerunner 165', 'Item Dimensions L x W': '10L x 6W centimetres', 'Unit Count': '2.0 unité', 'Number of Items': '2', 'Material': 'Silicone', 'Brand Name': 'TUTUO', 'Model Number': 'GM 165-HS+TM', 'Model Name': 'GM 165-HS+TM', 'Colour': 'Transparent/Green', 'Manufacturer': 'TUTUO', 'Part Number': 'GM 165-HS+TM', 'Best Sellers Rank': '4,130 in Electronics (See Top 100 in Electronics) 8 in Smartwatch Cases', 'ASIN': 'B0GHNJ6ZY3', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (61)   \n\n\n 4.4 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'GM 165', 'Compatible Phone Models': 'Garmin Forerunner 165, Garmin Forerunner 165 Music', 'Special Features': 'Effective protective TPU material, full protection', 'Clarity': '10', 'Compatible Wearable Computer Models': 'Garmin Forerunner 165', 'Item Dimensions L x W': '10L x 6W centimetres', 'Unit Count': '2.0 unité', 'Number of Items': '2', 'Material': 'Silicone', 'Brand Name': 'TUTUO', 'Model Number': 'GM 165-HS+TM', 'Model Name': 'GM 165-HS+TM', 'Colour': 'Transparent/Green', 'Manufacturer': 'TUTUO', 'Part Number': 'GM 165-HS+TM', 'Best Sellers Rank': '4,130 in Electronics (See Top 100 in Electronics) 8 in Smartwatch Cases', 'ASIN': 'B0GHNJ6ZY3', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (61)   \n\n\n 4.4 out of 5 stars'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7800,50 +7820,50 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[3 Pieces] Kamita Case Compatible with Garmin Vivoactive 5, Complete Protective Case with Tempered Glass Screen Protector, Shockproof Hard PC Bumper Case for Garmin Vivo Active 5 (Clear+Pink+White)</t>
+          <t>4.2 out of 5 stars</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.2 out of 5 stars</t>
+          <t>(192)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>(192)</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
           <t>COMPATIBILITY: This specially designed Kamita protective case is compatible with Garmin Vivoactive 5, which can provide full protection for your watch. The screen protectors and protective case fit your watch perfectly. NOTE: This case does not fit other watch models. Please check the model of your watch before purchasing. | New material: This case compatible with Garmin Vivoactive 5 is made of hard and durable PC, which is more resistant to wear and does not lose its colors. The smooth surface ensures smooth gliding and tactile sensitivity, which gives you a better touch feeling. | Total protection: our Garmin Vivo Active 5 hard PC cases can cover all sides of your watch, ensuring total protection for your watch. Shockproof and scratch resistant design protects the watch from bumps and scratches. | Precise cutouts and easy installation: Our watch cover has a precise button cut-out that allows it to snap into place quickly and fit your watch precisely. Allows easy access to all buttons, sound holes, sensors and smartwatch functions. What's more, the snap-on design is easy to install and remove without any tools. It is also not necessary to remove the case to charge. | Package includes: The package includes 3 pieces of covers for Garmin Vivo Active 5. Humanized ergonomic house, air cushion technology to protect all areas. Suitable for men, women, girls, boys and any occasion.</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="J10" t="n">
         <v>7</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatches', 'Form Factor': 'Case', 'Product Features': 'Shock and scratch resistant', 'Compatible Phone Models': 'Garmin Vivoactive 5', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Transparent+Pink+White', 'Shell Type': 'Hard', 'Enclosure Material': 'Polycarbonate', 'Brand Name': 'Kamita', 'Unit Count': '3.0 count', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '4,168 in Electronics (See Top 100 in Electronics) 9 in Smartwatch Cases', 'ASIN': 'B0DSZLRYTB', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (192)   \n\n\n 4.2 out of 5 stars', 'Item Dimensions': '8 x 1 x 1.3 centimetres'}</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Smartwatches', 'Form Factor': 'Case', 'Product Features': 'Shock and scratch resistant', 'Compatible Phone Models': 'Garmin Vivoactive 5', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Transparent+Pink+White', 'Shell Type': 'Hard', 'Enclosure Material': 'Polycarbonate', 'Brand Name': 'Kamita', 'Unit Count': '3.0 count', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '4,168 in Electronics (See Top 100 in Electronics) 9 in Smartwatch Cases', 'ASIN': 'B0DSZLRYTB', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (192)   \n\n\n 4.2 out of 5 stars', 'Item Dimensions': '8 x 1 x 1.3 centimetres'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="N10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7878,50 +7898,50 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Amizee 2 in 1 Case Compatible with Apple Watch Series 11/10 46mm, Hard Metal Material Full Protection Rugged Anti-Scratch Case for iWatch 46mm, Black</t>
+          <t>4.1 out of 5 stars</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.1 out of 5 stars</t>
+          <t>(1,683)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>(1,683)</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
           <t>【Compatible Models】Amizee cover only compatible with Apple Watch Series 11 (2025)/Series 10 46mm Cover. Note: Not suitable for other models and other types for smartwatch. Please confirm your watch size before placing an order. | 【Ultra 3/2/1 Second Change】Simple and tool-free installation transforms the appearance of your watch in seconds, allowing you to enjoy the Ultra 3/2/1 wearing experience, providing a stylish yet functional design and giving you a personal experience. The right button of the case has an updated built-in watch crown cover. (Note: crown does not work for ECG) | 【High quality metal casing】Made of high quality shockproof metal aluminum. Brighten up your Apple Watch and provide full protection without sacrificing beauty, and has long lasting protection against shocks. The snap-on design of the case is easy to install and remove. Charge directly, without removing the case. | 【Metal Bezel Protection】Raised edges around the screen for extra protection of the Apple Watch screen from scratches, bumps and accidental drops. Featuring an aluminum alloy frame, you will feel sturdy from the inside. (Note: does not include the built-in screen protector) | 【What you get】1 x black apple watch case 46 mm. If you have any defects or quality problems of our Apple Watch cases, please feel free to contact us, our customer service will reply you within 24 hours.</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="J11" t="n">
         <v>6</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Apple Watch Series 10 46mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '46 Millimetres', 'Product Features': 'Heavy Duty Protection', 'Compatible Phone Models': 'Apple Watch Series 11(2025)/Series 10 46mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black', 'Pattern': 'Sports', 'Theme': 'Sport', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Unit Count': '1.0 count', 'Manufacturer Part Number': 'BENQ3-CASE', 'Model Number': 'BENQ3-CASE', 'Manufacturer': 'Amizee', 'Age Range Description': 'Adult', 'Best Sellers Rank': '4,237 in Electronics (See Top 100 in Electronics) 10 in Smartwatch Cases', 'ASIN': 'B0DLKLY2RS', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (1,683)   \n\n\n 4.1 out of 5 stars', 'Item Dimensions': '11 x 45 x 50 millimetres'}</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Apple Watch Series 10 46mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '46 Millimetres', 'Product Features': 'Heavy Duty Protection', 'Compatible Phone Models': 'Apple Watch Series 11(2025)/Series 10 46mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black', 'Pattern': 'Sports', 'Theme': 'Sport', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Unit Count': '1.0 count', 'Manufacturer Part Number': 'BENQ3-CASE', 'Model Number': 'BENQ3-CASE', 'Manufacturer': 'Amizee', 'Age Range Description': 'Adult', 'Best Sellers Rank': '4,237 in Electronics (See Top 100 in Electronics) 10 in Smartwatch Cases', 'ASIN': 'B0DLKLY2RS', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (1,683)   \n\n\n 4.1 out of 5 stars', 'Item Dimensions': '11 x 45 x 50 millimetres'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="N11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7956,50 +7976,50 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Amizee 2 in 1 Metal Case Compatible with Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47mm, Ultra Thin Hard PC Bumper Anti-Scratch Protective Case for Galaxy Watch 7/8 Ultra, Blue/White</t>
+          <t>4.5 out of 5 stars</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.5 out of 5 stars</t>
+          <t>(907)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>(907)</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
           <t>Compatible models: Amizee cover only compatible with Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47 mm. Note: Not suitable for other models and other types for smartwatch. Please confirm your watch size before placing an order. | 【High Quality Metal Casing】Made of high quality impact-resistant aluminum, metal and PC material. Brighten up your Samsung Galaxy Watch and ensure full protection without sacrificing beauty, and features long lasting protection against bumps. | 【Metal Bezel Protection】Raised edges around the screen provide extra protection for the Samsung Galaxy Watch screen from scratches, bumps and accidental drops. Featuring an aluminum alloy frame, you will feel sturdy from the inside. (Note: Does not include a built-in screen protector.) | 【Easy to snap on】 The snap-on design of the case is easy to install and remove. Simply press the side of the back cover case into the alignment of the crown hole. No tools, without removing the Galaxy Watch. Charge directly, without removing the case. Snap button design on the back prevents the watch from falling off. | 【What you get】1 x Blue/White Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47 mm cover. If you have any defects or quality problems of our Apple Watch cases, please feel free to contact us, our customer service will reply you within 24 hours.</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="J12" t="n">
         <v>7</v>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '47 Millimetres', 'Product Features': 'Kickstand, Protection for demanding use, Wireless', 'Compatible Phone Models': 'Samsung Galaxy Watch Ultra/Ultra 2(2025) 47mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Blue / white', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Manufacturer Part Number': 'GALAXYCASE-BK', 'Model Number': 'SGUltra-CASE-BUWhite', 'Manufacturer': 'Amizee', 'Best Sellers Rank': '4,485 in Electronics (See Top 100 in Electronics) 11 in Smartwatch Cases', 'ASIN': 'B0GCHZ4RP5', 'Customer Reviews': '4.5  4.5 out of 5 stars   \n    (907)   \n\n\n 4.5 out of 5 stars', 'Item Dimensions': '48 x 46 x 16 millimetres', 'Item Weight': '0.47 Ounces'}</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '47 Millimetres', 'Product Features': 'Kickstand, Protection for demanding use, Wireless', 'Compatible Phone Models': 'Samsung Galaxy Watch Ultra/Ultra 2(2025) 47mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Blue / white', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Manufacturer Part Number': 'GALAXYCASE-BK', 'Model Number': 'SGUltra-CASE-BUWhite', 'Manufacturer': 'Amizee', 'Best Sellers Rank': '4,485 in Electronics (See Top 100 in Electronics) 11 in Smartwatch Cases', 'ASIN': 'B0GCHZ4RP5', 'Customer Reviews': '4.5  4.5 out of 5 stars   \n    (907)   \n\n\n 4.5 out of 5 stars', 'Item Dimensions': '48 x 46 x 16 millimetres', 'Item Weight': '0.47 Ounces'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8034,50 +8054,50 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ivoler 3 Pieces Case with Screen Protector for Huawei Watch GT 5 46mm, Full Protective Soft TPU Thin Shockproof Anti-Scratch Cover Case (2 Transparent + 1 Black)</t>
+          <t>4.3 out of 5 stars</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.3 out of 5 stars</t>
+          <t>(361)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>(361)</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
           <t>[Applicable Model]---- Compatible with Huawei Watch GT 5 46mm (Not for Huawei Watch GT 5 41mm). This case is designed with precise cutouts for functional buttons, speaker hole, charging hole, etc.(The package only contains cases, watch and watch band are not included!) | [Full Protection] --- Our case covers the full front and curved edges of the watch, provides complete protection of your watch against dust, fingerprints, scratches, drops or bumps to the ground. | [Sensitive Touch and High Transparency]---- Made of premium TPU material, smooth, transparent and without influencing touch sensitivity. Gives you original touch sensitivity and high touch responsiveness. Hydrophobic and oleophobic screen coating can easily separate oil, fingerprints and other stains, make the screen easy to clean, prevent your watch screens from looking shabby and dull. | [Ultra Slim and Easy to Install] ---- Ultra thin and lightweight, never be a burden on your wrist from your work to your workout. Easy to wear and remove and designed to be compatible with the charger, you don't need to remove the protective case when charging. | [What you get] --- 3 x iVoler cases with built-in screen protector (2 transparent + 1 black). [Warm Tip]: Using this product in the gym or during sports activities may cause moisture (sweating) to build up between this product and the monitor screen. Use dry cloth to keep it dry if you have water, if you have any questions or product problems, please contact us, we will do the best service for you.</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'huawei watch gt 5 46mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'huawei watch gt 5 46mm', 'Special Features': 'Rounded Edge, Shockproof', 'Screen Size': '46 Millimetres', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Compatible Wearable Computer Models': 'Huawei WATCH GT, SUUNTO 5', 'Unit Count': '3.0 count', 'Number of Items': '3', 'Brand Name': 'ivoler', 'Model Name': 'iVoler Huawei Watch GT 5 46mm Screen Protector', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00039', 'Best Sellers Rank': '3,967 in Electronics (See Top 100 in Electronics) 12 in Smartwatch Cases', 'ASIN': 'B0DJTDNSQN', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (361)   \n\n\n 4.3 out of 5 stars', 'Material': 'Silicone'}</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'huawei watch gt 5 46mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'huawei watch gt 5 46mm', 'Special Features': 'Rounded Edge, Shockproof', 'Screen Size': '46 Millimetres', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Compatible Wearable Computer Models': 'Huawei WATCH GT, SUUNTO 5', 'Unit Count': '3.0 count', 'Number of Items': '3', 'Brand Name': 'ivoler', 'Model Name': 'iVoler Huawei Watch GT 5 46mm Screen Protector', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00039', 'Best Sellers Rank': '3,967 in Electronics (See Top 100 in Electronics) 12 in Smartwatch Cases', 'ASIN': 'B0DJTDNSQN', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (361)   \n\n\n 4.3 out of 5 stars', 'Material': 'Silicone'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8112,50 +8132,50 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Amizee 2 in 1 Case [2 Pieces] Compatible with Apple Watch SE 3/2/1 Series 6/5/4 40mm with Screen Protector, Full Coverage Anti-Scratch Case Cover for iWatch 40mm (Black)</t>
+          <t>4.1 out of 5 stars</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.1 out of 5 stars</t>
+          <t>(3,036)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>(3,036)</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
           <t>【Compatible Models】Designed for Apple Watch SE 3/2/1 Series 6/5/4 40mm. NOTE: Not suitable for other models and other types of smartwatch. Please confirm your watch size before placing an order. | 【Full Body Protection】Made of high quality hard PC material, with built-in screen protector. 2 in 1 design provides robust 360 degree protection. Full body protection keeps your Apple Watch 40mm from scratches and drops. | High sensitivity touch: The high-transparency tempered glass screen protector provides original vision and touch experience; Ultra-thin, three-dimensional right-angle edge, the design is slimmer. | 【Precise Fit】Sensitive button covers allow responsive pressing; Easy access to Apple Watch button and functions with precise cutouts; Easy to install, charge directly, without removing the case. | 【WHAT YOU GET】2 x Black Apple Watch Case 40 mm; We offer a one-year warranty, please feel free to contact us for any problem, a satisfactory solution is promised forever.</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="J14" t="n">
         <v>6</v>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Apple Watch Series 6/5/4/SE 40mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'Apple Watch', 'Special Features': 'Robust protection, Scratch Resistant, Shockproof, screen protector', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Waterproof', 'Screen Size': '44 Millimetres', 'Screen Surface Description': 'Matte', 'Clarity': '0.99', 'Compatible Wearable Computer Models': 'Apple Watch SE 40mm', 'Item Dimensions L x W': '43L x 38W millimetres', 'Unit Count': '1.0 unité', 'Number of Items': '2', 'Brand Name': 'Amizee', 'Model Number': 'APPLECASE-ZB', 'Model Name': 'CAZB-40-BLC', 'Colour': 'Black / Black', 'Manufacturer': 'Amizee', 'Part Number': 'CAZB-40-BLC', 'Item Weight': '0.18 Ounces', 'Included Components': 'Case for Apple Watch 40mm', 'Best Sellers Rank': '3,327 in Electronics (See Top 100 in Electronics) 13 in Smartwatch Cases 92 in Smartwatch Screen Protectors &amp; Foils', 'ASIN': 'B0C2CM7QWR', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (3,036)   \n\n\n 4.1 out of 5 stars', 'Material': 'Polycarbonate, Tempered Glass'}</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Apple Watch Series 6/5/4/SE 40mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'Apple Watch', 'Special Features': 'Robust protection, Scratch Resistant, Shockproof, screen protector', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Waterproof', 'Screen Size': '44 Millimetres', 'Screen Surface Description': 'Matte', 'Clarity': '0.99', 'Compatible Wearable Computer Models': 'Apple Watch SE 40mm', 'Item Dimensions L x W': '43L x 38W millimetres', 'Unit Count': '1.0 unité', 'Number of Items': '2', 'Brand Name': 'Amizee', 'Model Number': 'APPLECASE-ZB', 'Model Name': 'CAZB-40-BLC', 'Colour': 'Black / Black', 'Manufacturer': 'Amizee', 'Part Number': 'CAZB-40-BLC', 'Item Weight': '0.18 Ounces', 'Included Components': 'Case for Apple Watch 40mm', 'Best Sellers Rank': '3,327 in Electronics (See Top 100 in Electronics) 13 in Smartwatch Cases 92 in Smartwatch Screen Protectors &amp; Foils', 'ASIN': 'B0C2CM7QWR', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (3,036)   \n\n\n 4.1 out of 5 stars', 'Material': 'Polycarbonate, Tempered Glass'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8190,50 +8210,50 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4-Piece Case Compatible with Xiaomi Redmi Watch 5 Active, Hard PC Case with Screen Protector, HD Case with Tempered Glass – Transparent, Black, Pink, Blue</t>
+          <t>4.2 out of 5 stars</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.2 out of 5 stars</t>
+          <t>(540)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>(540)</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
           <t>1. Compatible models: Only compatible with Xiaomi Redmi Watch 5 Active, please confirm your watch model before purchasing. 4 colours per pack: transparent, black, pink, blue. | 2. Full protection: It protects the watch screen and sides from scratches, scrapes, chips, collisions or other damage. | 3. Material: durable PC case with screen protector. No influence on touch sensitivity, sensor functions work well with watch case. | 4. Easy to install: its snap-on design to avoid peeling off. Precise hole cutouts make it easy to access all buttons or buttons, slim and lightweight, no need to remove the watch case when charging. | 5. Tips: Recommended for removing the case when swimming or bathing. Moisture can be trapped in case when you exercise, please use the microfiber cloth to wipe it.</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="J15" t="n">
         <v>5</v>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Xiaomi Redmi Watch 5 Active', 'Special Features': 'High quality tempered glass', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Not Water Resistant', 'Screen Surface Description': 'Glossy', 'Clarity': '10', 'Unit Count': '4.0 count', 'Number of Items': '4', 'Material': 'Polycarbonate', 'Brand Name': 'Bigqin', 'Model Number': '13XMRMW5A-4PC', 'Model Name': 'Xiaomi Redmi Watch 5 Active Screen Protector 4-Pack', 'Customer Package Type': 'FFP Packaging', 'Colour': 'Redmi Watch 5 Active', 'Manufacturer': 'Bigqin', 'Part Number': 'B02', 'Included Components': 'Watch', 'Best Sellers Rank': '4,821 in Electronics (See Top 100 in Electronics) 14 in Smartwatch Cases', 'ASIN': 'B0DM4WJ7XH', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (540)   \n\n\n 4.2 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Xiaomi Redmi Watch 5 Active', 'Special Features': 'High quality tempered glass', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Not Water Resistant', 'Screen Surface Description': 'Glossy', 'Clarity': '10', 'Unit Count': '4.0 count', 'Number of Items': '4', 'Material': 'Polycarbonate', 'Brand Name': 'Bigqin', 'Model Number': '13XMRMW5A-4PC', 'Model Name': 'Xiaomi Redmi Watch 5 Active Screen Protector 4-Pack', 'Customer Package Type': 'FFP Packaging', 'Colour': 'Redmi Watch 5 Active', 'Manufacturer': 'Bigqin', 'Part Number': 'B02', 'Included Components': 'Watch', 'Best Sellers Rank': '4,821 in Electronics (See Top 100 in Electronics) 14 in Smartwatch Cases', 'ASIN': 'B0DM4WJ7XH', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (540)   \n\n\n 4.2 out of 5 stars'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8268,50 +8288,50 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ivoler 3 Pieces Case with Screen Protector for Amazfit Active 2 (Round Edition), Full Protective Soft TPU Slim Shockproof Anti-Scratch Cover (2 Transparent + 1 Black)</t>
+          <t>4.3 out of 5 stars</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.3 out of 5 stars</t>
+          <t>(90)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>(90)</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
           <t>[Applicable Model]---- Compatible with Amazfit Active 2 (Round Edition) (Not for Amazfit Active 2 Square Edition). This case is designed with precise cutouts for functional buttons, speaker hole, charging hole, etc.(The package only contains cases, watch and watch band are not included!) | [Full Protection] --- Our case covers the full front and curved edges of the watch, provides complete protection of your watch against dust, fingerprints, scratches, drops or bumps to the ground. | [Sensitive Touch and High Transparency]---- Made of premium TPU material, smooth, transparent and without influencing touch sensitivity. Gives you original touch sensitivity and high touch responsiveness. Hydrophobic and oleophobic screen coating can easily separate oil, fingerprints and other stains, make the screen easy to clean, prevent your watch screens from looking shabby and dull. | [Ultra Slim and Easy to Install] ---- Ultra thin and lightweight, never be a burden on your wrist from your work to your workout. Easy to wear and remove and designed to be compatible with the charger, you don't need to remove the protective case when charging. | [What you get] --- 3 x iVoler cases with built-in screen protector (2 transparent + 1 black). [Warm Tip]: Using this product in the gym or during sports activities may cause moisture (sweating) to build up between this product and the monitor screen. Use dry cloth to keep it dry if you have water, if you have any questions or product problems, please contact us, we will do the best service for you.</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="J16" t="n">
         <v>7</v>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active 2 (Round Edition)', 'Special Features': 'Rounded Edge, Shockproof', 'Finish Type': 'Glossy', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Item Dimensions L x W': '7.2L x 8.2W centimetres', 'Unit Count': '1.0 unité', 'Number of Items': '3', 'Material': 'Silicone', 'Brand Name': 'ivoler', 'Model Name': 'Amazfit Active 2 (Round Edition) Screen Protector', 'Colour': '2 Transparent + 1 Black', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00073', 'Product Warranty': '1', 'Included Components': 'Case', 'Best Sellers Rank': '4,873 in Electronics (See Top 100 in Electronics) 15 in Smartwatch Cases', 'ASIN': 'B0DSW4V65Z', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (90)   \n\n\n 4.3 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active 2 (Round Edition)', 'Special Features': 'Rounded Edge, Shockproof', 'Finish Type': 'Glossy', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Item Dimensions L x W': '7.2L x 8.2W centimetres', 'Unit Count': '1.0 unité', 'Number of Items': '3', 'Material': 'Silicone', 'Brand Name': 'ivoler', 'Model Name': 'Amazfit Active 2 (Round Edition) Screen Protector', 'Colour': '2 Transparent + 1 Black', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00073', 'Product Warranty': '1', 'Included Components': 'Case', 'Best Sellers Rank': '4,873 in Electronics (See Top 100 in Electronics) 15 in Smartwatch Cases', 'ASIN': 'B0DSW4V65Z', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (90)   \n\n\n 4.3 out of 5 stars'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8326,34 +8346,64 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8368,34 +8418,64 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8410,34 +8490,64 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8452,34 +8562,64 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8494,34 +8634,64 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8536,34 +8706,64 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8578,34 +8778,64 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8620,34 +8850,64 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8662,34 +8922,64 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8704,34 +8994,64 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8746,34 +9066,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Visit the Miimall Store</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>5105</v>
+      </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>[Compatibility] Perfectly compatible with Apple Watch Ultra 49mm. (This case does not come with a screen protector)</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>[TPU Material] This shockproof TPU case is soft, flexible and durable and provides long-lasting impact protection you can rely on.</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>[Easy to Put on and Remove] This Apple Watch Ultra 49mm case is equipped with precise cutouts that allow easy access to all controls, buttons, sensors and watch functions. Does not interfere with bezel rotation and other watch functions, easy to put on and take off, this case does not need to be removed when charging.</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>[PC Keys Design] Comes with PC button, allows you to use more easily. Precise cut, easy access to all controls, buttons, sensors and functions.</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>[No Screen Protector] The Apple Watch 49mm protective case is not equipped with a protective film. Supports use with other screen protectors.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8788,34 +9158,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Diruite</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>98</v>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Xiaomi Smart Band 10', 'Form Factor': 'Cover', 'Product Features': 'Kratzfest', 'Compatible Phone Models': 'Xiaomi Smart Band 10', 'Colour': 'Black&amp;Black&amp;Black', 'Shell Type': 'Soft', 'Enclosure Material': 'Thermoplastic Polyurethane', 'Brand Name': 'Diruite', 'Unit Count': '3.0 count', 'Manufacturer': 'Diruite', 'Best Sellers Rank': '5,917 in Electronics (See Top 100 in Electronics) 27 in Smartwatch Cases', 'ASIN': 'B0FFYWVP45', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (98)   \n\n\n 4.4 out of 5 stars', 'Item Weight': '20 Grams'}</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Compatible models: this soft TPU case is specially designed screen protector for Xiaomi Smart Band 10 and offers full protection without slots. Ultra soft texture effectively protects your watch from scratches, bumps and drops.</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>High fit: The soft case cover precisely fits the Xiaomi Smart Band 10 perfectly without compromising the normal operation and operation of the watch, while providing a comfortable feel.</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Shock and drop resistance: The elasticity and cushioning of the TPU material provide effective protection against internal damage when your Xiaomi Smart Band 10 is touched.</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>High sensitivity touch control: The Xiaomi Smart Band 10 watch protective case is equipped with a high-resolution screen protector that does not affect the usability of the screen and maintains the touch sensitivity of the watch and monitor, presenting crisp and original image quality and original touch sensitivity.</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Easy installation: precisely matches all the holes in the watch of your Xiaomi Smart Band 10. Screen Protectors for Xiaomi Smart Band 10*3</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8830,34 +9250,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>GIOPUEY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Warm tip: Please check that the model or size of your device is compatible with this product before buying. If you have any questions, please feel free to consult them.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>32</v>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Amazfit Active Max', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active Max', 'Special Features': '9 H Surface Hardness', 'Screen Surface Description': 'Hard', 'Clarity': '9', 'Compatible Wearable Computer Models': 'Amazfit Active', 'Unit Count': '2.0 count', 'Number of Items': '2', 'Material': 'Plastic Glass', 'Brand Name': 'GIOPUEY', 'Model Number': 'GIOPUEY', 'Colour': '2 x black', 'Manufacturer': 'GIOPUEY', 'Part Number': 'Amazfit Active Max', 'Item Weight': '10 Grams', 'Best Sellers Rank': '5,952 in Electronics (See Top 100 in Electronics) 28 in Smartwatch Cases', 'ASIN': 'B0G6C44RPY', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (32)   \n\n\n 4.1 out of 5 stars'}</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Easy to install: you can install the housing easily. It does not affect the load after installation.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Material: hard plastic + tempered glass</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Anti-Scratch The protective case with built-in 9H tempered glass can effectively protect your watch from daily scratches and bumps.</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>TOUCH SENSITIVE - Ultra thin tempered glass screen protector retains the original sensitive touch of the watch and ensures a quick launch of the app.</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Access to all functions: Direct charging without removing the case and strap. Precise cutouts for easy access to all function buttons.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8872,34 +9342,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>Kamita</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Aucune description</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>68</v>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Garmin Vivoactive 6', 'Form Factor': 'Case', 'Product Features': 'Scratch Resistant, Shockproof', 'Compatible Phone Models': 'Garmin Vivoactive 6', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Clear*3', 'Shell Type': 'Hard', 'Enclosure Material': 'Tempered Glass', 'Brand Name': 'Kamita', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '6,152 in Electronics (See Top 100 in Electronics) 29 in Smartwatch Cases', 'ASIN': 'B0F6LP1M79', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (68)   \n\n\n 4.2 out of 5 stars'}</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>COMPATIBILITY: This specially designed Kamita protective case is compatible with Garmin Vivoactive 6, which can provide full protection for your watch. The screen protectors and protective case fit your watch perfectly. NOTE: This case does not fit other watch models. Please check the model of your watch before purchasing.</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>New material: This case compatible with Garmin Vivoactive 6 is made of hard and durable PC, which is more resistant to wear and does not lose its colors. The smooth surface ensures smooth gliding and tactile sensitivity, which gives you a better touch feeling.</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Total protection: our Garmin Vivo Active 6 hard PC cases can cover all sides of your watch, ensuring total protection for your watch. Shockproof and scratch resistant design protects the watch from bumps and scratches.</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Precise cutouts and easy installation: Our watch cover has a precise button cut-out that allows it to snap into place quickly and fit your watch precisely. Allows easy access to all buttons, sound holes, sensors and smartwatch functions. What's more, the snap-on design is easy to install and remove without any tools. It is also not necessary to remove the case to charge.</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Package includes: The package includes 3 pieces of covers for Garmin Vivo Active 6. Humanized ergonomic house, air cushion technology to protect all areas. Suitable for men, women, girls, boys and any occasion.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8914,34 +9434,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>GIOPUEY</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Warm tip: Please check that the model or size of your device is compatible with this product before buying. If you have any questions, please feel free to consult them.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>À collecter en Phase 2</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>74</v>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Garmin Venu 4 45mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '45 Millimetres', 'Compatible Phone Models': 'Garmin Venu 4 45mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black x 2', 'Shell Type': 'Soft', 'Enclosure Material': 'Silicone', 'Item Dimensions': '2 x 2 x 2 millimetres', 'Item Weight': '10 Grams', 'Brand Name': 'GIOPUEY', 'Unit Count': '2.0 count', 'Manufacturer Part Number': 'Garmin Venu 4 45mm', 'Model Number': 'GIOPUEY', 'Manufacturer': 'GIOPUEY', 'Best Sellers Rank': '6,206 in Electronics (See Top 100 in Electronics) 30 in Smartwatch Cases', 'ASIN': 'B0GDJSFDL4', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (74)   \n\n\n 4.4 out of 5 stars'}</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Package includes: 2 x Silicone Protective Case</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>NO INTERFERENCE WITH SCREEN - The semi-wrap design leaves the screen fully exposed and does not interfere with the touch operation of the watch or the screen display, allowing you to use the features of the anywhere, anytime.</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Perfect Fit: Precise cutting and fitting technology ensures that the case fits your perfectly without interfering with the watch's operation, charging and wearing, allowing you to enjoy a comfortable and pleasant using experience.</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>One-Step Installation: Thanks to the one-step installation design, there is no need for tools or complicated steps, just gently slip on the case to complete the installation.</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>QUALITY SERVICE: If you have any questions or needs, please feel free to contact our customer service team, we will try our best to solve your problems and ensure your satisfaction.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8984,6 +9554,10 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9026,6 +9600,10 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9068,6 +9646,10 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9110,6 +9692,10 @@
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9152,6 +9738,10 @@
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9194,6 +9784,10 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9236,6 +9830,10 @@
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9278,6 +9876,10 @@
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9320,6 +9922,10 @@
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9362,6 +9968,10 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9404,6 +10014,10 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9446,6 +10060,10 @@
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9488,6 +10106,10 @@
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9530,6 +10152,10 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9572,6 +10198,10 @@
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9614,6 +10244,10 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9656,6 +10290,10 @@
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9698,6 +10336,10 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9740,6 +10382,10 @@
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9782,6 +10428,10 @@
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7046,6 +7046,2206 @@
         </is>
       </c>
       <c r="D301" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>B0CNVTCK51</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>€9.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>B0CNVTCK51</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>€9.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>B0BPNT6XYY</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>B0BPNT6XYY</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>B0F93BDHHF</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>€22.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>B0F93BDHHF</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>€22.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>B0DJS84VNY</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>B0DJS84VNY</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>B0DWXHV7L5</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>B0DWXHV7L5</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>€7.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>B0F6MRMCCQ</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>B0F6MRMCCQ</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>B0FXFX6W31</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>#14</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>B0FXFX6W31</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>€9.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>#15</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>B0GHNJ6ZY3</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>€9.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>#16</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>B0GHNJ6ZY3</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>€9.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>#17</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>B0DSZLRYTB</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>#18</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>B0DSZLRYTB</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>#19</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>B0DLKLY2RS</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>#20</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>B0DLKLY2RS</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>#21</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>B0GCHZ4RP5</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>#22</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>B0GCHZ4RP5</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>#23</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>B0DJTDNSQN</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>#24</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>B0DJTDNSQN</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>#25</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>B0C2CM7QWR</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>€14.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>#26</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>B0C2CM7QWR</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>€14.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>#27</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>B0DM4WJ7XH</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>#28</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>B0DM4WJ7XH</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>#29</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>B0DSW4V65Z</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>#30</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>B0DSW4V65Z</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>#31</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>B0DSZXH6BG</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>#32</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>B0DSZXH6BG</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>#33</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>B0DWSTJ4HS</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>€17.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>#34</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>B0DWSTJ4HS</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>€17.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>#35</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>B0DK8SYX8F</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>€9.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>#36</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>B0DK8SYX8F</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>€9.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>#37</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>B0DK9528FW</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>€9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>B0DK9528FW</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>€9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>#39</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>B0CFV96666</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>#40</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>B0CFV96666</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>#41</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>B0F9YKRBCJ</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>#42</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>B0F9YKRBCJ</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>#43</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>B0D7YT3ZMX</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>#44</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>B0D7YT3ZMX</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>€8.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>#45</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>B0CYGJ2RNV</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>€9.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>#46</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>B0CYGJ2RNV</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>€9.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>#47</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>B0F2MV5NGP</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>#48</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>B0F2MV5NGP</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>#49</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>B0FXG8CR1V</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>#50</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>B0FXG8CR1V</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>€9.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>#51</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>B0BTH76GS7</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>€10.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>#52</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>B0BTH76GS7</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>€10.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>#53</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>B0FFYWVP45</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>€11.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>#54</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>B0FFYWVP45</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>€11.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>#55</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>B0G6C44RPY</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>#56</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>B0G6C44RPY</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>#57</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>B0F6LP1M79</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>#58</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>B0F6LP1M79</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>€11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>#59</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>B0GDJSFDL4</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>#60</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>B0GDJSFDL4</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>#61</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>B0F6CNSRNC</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>#62</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>B0F6CNSRNC</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>#63</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>B0FFSF5NHR</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>#64</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>B0FFSF5NHR</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>#65</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>B0FXX82RGG</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>€17.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>#66</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>B0FXX82RGG</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>€17.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>#67</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>B0GJN22NJV</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>#68</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>B0GJN22NJV</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>#69</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>B0FVL3BV29</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>#70</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>B0FVL3BV29</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>€21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>#71</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>B0DFPRVGN7</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>€5.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>#72</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>B0DFPRVGN7</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>€5.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>#73</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>B0FDKND69M</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>€13.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>#74</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>B0FDKND69M</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>€13.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>#75</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>B0DM5YLYHB</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>#76</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>B0DM5YLYHB</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>#77</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>B0D5JRJCVX</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>€12.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>#78</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>B0D5JRJCVX</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>€12.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>#79</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>B0GF6SBD6J</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>#80</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>B0GF6SBD6J</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>#81</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>B0G3WZMGZJ</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>€6.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>#82</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>B0G3WZMGZJ</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>€6.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>#83</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>B0DDSPNKNT</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Non communiqué</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>#84</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>B0DDSPNKNT</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Non communiqué</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>#85</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>B0FJY96R5S</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>#86</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>B0FJY96R5S</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>#87</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>B0DJTD19WX</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>#88</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>B0DJTD19WX</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>#89</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>B0FPF2PBNM</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>#90</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>B0FPF2PBNM</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>€7.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>#91</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>B0D8KHVX7S</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>€10.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>#92</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>B0D8KHVX7S</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>€10.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>#93</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>B0CCND87VQ</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>€8.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>#94</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>B0CCND87VQ</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>€8.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>#95</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>B0F2GHWNK3</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>#96</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>B0F2GHWNK3</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>€6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>#97</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>B0DXZZKPQ3</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>#98</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>B0DXZZKPQ3</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>€7.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>#99</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>B0F5B537XQ</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>€10.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>#100</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>B0F5B537XQ</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
         <is>
           <t>€10.99</t>
         </is>
@@ -7062,7 +9262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7088,80 +9288,75 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Attributs</t>
+          <t>Date_Detection</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Date_Detection</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Nb_Avis</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Nb_Avis</t>
+          <t>Bullet_Points</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Bullet_Points</t>
+          <t>Nombre_Images</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Nombre_Images</t>
+          <t>Caracteristiques</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Caracteristiques</t>
+          <t>BSR_Categories</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>BSR_Categories</t>
+          <t>Declinaisons</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Declinaisons</t>
+          <t>Nb_Declinaisons</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Nb_Declinaisons</t>
+          <t>Date_Analyse</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Date_Analyse</t>
+          <t>Bullet_1</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Bullet_1</t>
+          <t>Bullet_2</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Bullet_2</t>
+          <t>Bullet_3</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Bullet_3</t>
+          <t>Bullet_4</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Bullet_4</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Bullet_5</t>
         </is>
@@ -7185,65 +9380,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aucune description textuelle</t>
+          <t>Aucune description</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
           <t>Aucun</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="I2" t="n">
         <v>1</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Aucune caractéristique trouvée</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7263,65 +9451,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aucune description textuelle</t>
+          <t>Aucune description</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
           <t>Aucun</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="I3" t="n">
         <v>1</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Aucune caractéristique trouvée</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7341,65 +9522,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Aucune description textuelle</t>
+          <t>Aucune description</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
           <t>Aucun</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="I4" t="n">
         <v>1</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Aucune caractéristique trouvée</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7419,65 +9593,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aucune description textuelle</t>
+          <t>Aucune description</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
           <t>Aucun</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="I5" t="n">
         <v>1</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Aucune caractéristique trouvée</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7497,65 +9664,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aucune description textuelle</t>
+          <t>Aucune description</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
           <t>Aucun</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="I6" t="n">
         <v>1</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Aucune caractéristique trouvée</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7575,65 +9735,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Aucune description textuelle</t>
+          <t>Aucune description</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
           <t>Aucun</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="I7" t="n">
         <v>1</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Aucune caractéristique trouvée</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7658,60 +9811,55 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>4.3 out of 5 stars</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.3 out of 5 stars</t>
+          <t>(2,040)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(2,040)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
           <t>【COMPATIBILITY】Tensea iWatch screen protector with back cover is designed to fit Apple Watch Ultra 3 49mm, Apple Watch Ultra 2 49mm and Apple Watch Ultra 49mm. The bumper cover built into the screen protector provides a perfect fit. | 【Daily Water Resistance】 Apple Watch Ultra 3/Ultra 2/Ultra 49mm has a built-in seal that effectively prevents water from entering the screen. Its exceptional water resistance for everyday use makes it possible to use it with confidence during activities such as showering, hand washing, sweating or showering. [Note: Not suitable for deep water environments such as diving or swimming.] | 【360°Protection】This protective case, compatible with the surface of iWatch Ultra 3/Ultra 2/Ultra 49mm, provides full protection to the front and back of your watch, effectively resisting dust, dirt, scratches and damage. The 9H tempered glass screen protector preserves touch sensitivity, while the sweat-resistant case design allows for easy installation without having to remove the band. | 【Upgraded Materials】 Scratch-resistant and impact-resistant tempered glass has a hardness of 9H. Shock absorbing polycarbonate provides superior rigidity, improved resilience and better protection compared to conventional TPU. Glass construction prevents fogging caused by temperature fluctuations. | 【Easy Installation】The product page includes installation video and the package contains installation instructions. A removal tool is provided to allow the watch case to be removed without damaging it.</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="I8" t="n">
         <v>7</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Aucune caractéristique trouvée</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7732,60 +9880,55 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>4.4 out of 5 stars</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.4 out of 5 stars</t>
+          <t>(61)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(61)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
           <t>Compatible Model: Compatible with Garmin Forerunner 165 / 165 Music. Precise design will fit your watch perfectly. (Note: Please check your watch model number before purchasing) | Full protection: The protective case for Garmin Forerunner 165 / 165 Music offers full screen protection from four sides to the corners. Slightly higher edges protect the surface of your watch and protect it from scratches, bumps and accidental drops. | Effective protective TPU material: made of high-quality and scratch-resistant TPU material. Soft and lightweight, very comfortable to wear, leaves no air bubbles between the case and the screen, giving you an original viewing experience and touch experience. | Easy to install: no tools required. You don't need to remove the case, just align the holes with the watch buttons and put the case in place. Precise cutouts for quick access to screen, button and sensor. The case does not need to be removed when charging. | Fashion and Light: Soft and thin TPU materials make it easy to put on and take off your watch. Slim and lightweight, never strain your wrist from work to exercise. Give you a better user experience.</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="I9" t="n">
         <v>7</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'GM 165', 'Compatible Phone Models': 'Garmin Forerunner 165, Garmin Forerunner 165 Music', 'Special Features': 'Effective protective TPU material, full protection', 'Clarity': '10', 'Compatible Wearable Computer Models': 'Garmin Forerunner 165', 'Item Dimensions L x W': '10L x 6W centimetres', 'Unit Count': '2.0 unité', 'Number of Items': '2', 'Material': 'Silicone', 'Brand Name': 'TUTUO', 'Model Number': 'GM 165-HS+TM', 'Model Name': 'GM 165-HS+TM', 'Colour': 'Transparent/Green', 'Manufacturer': 'TUTUO', 'Part Number': 'GM 165-HS+TM', 'Best Sellers Rank': '4,130 in Electronics (See Top 100 in Electronics) 8 in Smartwatch Cases', 'ASIN': 'B0GHNJ6ZY3', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (61)   \n\n\n 4.4 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'GM 165', 'Compatible Phone Models': 'Garmin Forerunner 165, Garmin Forerunner 165 Music', 'Special Features': 'Effective protective TPU material, full protection', 'Clarity': '10', 'Compatible Wearable Computer Models': 'Garmin Forerunner 165', 'Item Dimensions L x W': '10L x 6W centimetres', 'Unit Count': '2.0 unité', 'Number of Items': '2', 'Material': 'Silicone', 'Brand Name': 'TUTUO', 'Model Number': 'GM 165-HS+TM', 'Model Name': 'GM 165-HS+TM', 'Colour': 'Transparent/Green', 'Manufacturer': 'TUTUO', 'Part Number': 'GM 165-HS+TM', 'Best Sellers Rank': '4,130 in Electronics (See Top 100 in Electronics) 8 in Smartwatch Cases', 'ASIN': 'B0GHNJ6ZY3', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (61)   \n\n\n 4.4 out of 5 stars'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7810,60 +9953,55 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>4.2 out of 5 stars</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.2 out of 5 stars</t>
+          <t>(192)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(192)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
           <t>COMPATIBILITY: This specially designed Kamita protective case is compatible with Garmin Vivoactive 5, which can provide full protection for your watch. The screen protectors and protective case fit your watch perfectly. NOTE: This case does not fit other watch models. Please check the model of your watch before purchasing. | New material: This case compatible with Garmin Vivoactive 5 is made of hard and durable PC, which is more resistant to wear and does not lose its colors. The smooth surface ensures smooth gliding and tactile sensitivity, which gives you a better touch feeling. | Total protection: our Garmin Vivo Active 5 hard PC cases can cover all sides of your watch, ensuring total protection for your watch. Shockproof and scratch resistant design protects the watch from bumps and scratches. | Precise cutouts and easy installation: Our watch cover has a precise button cut-out that allows it to snap into place quickly and fit your watch precisely. Allows easy access to all buttons, sound holes, sensors and smartwatch functions. What's more, the snap-on design is easy to install and remove without any tools. It is also not necessary to remove the case to charge. | Package includes: The package includes 3 pieces of covers for Garmin Vivo Active 5. Humanized ergonomic house, air cushion technology to protect all areas. Suitable for men, women, girls, boys and any occasion.</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="I10" t="n">
         <v>7</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatches', 'Form Factor': 'Case', 'Product Features': 'Shock and scratch resistant', 'Compatible Phone Models': 'Garmin Vivoactive 5', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Transparent+Pink+White', 'Shell Type': 'Hard', 'Enclosure Material': 'Polycarbonate', 'Brand Name': 'Kamita', 'Unit Count': '3.0 count', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '4,168 in Electronics (See Top 100 in Electronics) 9 in Smartwatch Cases', 'ASIN': 'B0DSZLRYTB', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (192)   \n\n\n 4.2 out of 5 stars', 'Item Dimensions': '8 x 1 x 1.3 centimetres'}</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Smartwatches', 'Form Factor': 'Case', 'Product Features': 'Shock and scratch resistant', 'Compatible Phone Models': 'Garmin Vivoactive 5', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Transparent+Pink+White', 'Shell Type': 'Hard', 'Enclosure Material': 'Polycarbonate', 'Brand Name': 'Kamita', 'Unit Count': '3.0 count', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '4,168 in Electronics (See Top 100 in Electronics) 9 in Smartwatch Cases', 'ASIN': 'B0DSZLRYTB', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (192)   \n\n\n 4.2 out of 5 stars', 'Item Dimensions': '8 x 1 x 1.3 centimetres'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7888,60 +10026,55 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>4.1 out of 5 stars</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.1 out of 5 stars</t>
+          <t>(1,683)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(1,683)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
           <t>【Compatible Models】Amizee cover only compatible with Apple Watch Series 11 (2025)/Series 10 46mm Cover. Note: Not suitable for other models and other types for smartwatch. Please confirm your watch size before placing an order. | 【Ultra 3/2/1 Second Change】Simple and tool-free installation transforms the appearance of your watch in seconds, allowing you to enjoy the Ultra 3/2/1 wearing experience, providing a stylish yet functional design and giving you a personal experience. The right button of the case has an updated built-in watch crown cover. (Note: crown does not work for ECG) | 【High quality metal casing】Made of high quality shockproof metal aluminum. Brighten up your Apple Watch and provide full protection without sacrificing beauty, and has long lasting protection against shocks. The snap-on design of the case is easy to install and remove. Charge directly, without removing the case. | 【Metal Bezel Protection】Raised edges around the screen for extra protection of the Apple Watch screen from scratches, bumps and accidental drops. Featuring an aluminum alloy frame, you will feel sturdy from the inside. (Note: does not include the built-in screen protector) | 【What you get】1 x black apple watch case 46 mm. If you have any defects or quality problems of our Apple Watch cases, please feel free to contact us, our customer service will reply you within 24 hours.</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="I11" t="n">
         <v>6</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Apple Watch Series 10 46mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '46 Millimetres', 'Product Features': 'Heavy Duty Protection', 'Compatible Phone Models': 'Apple Watch Series 11(2025)/Series 10 46mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black', 'Pattern': 'Sports', 'Theme': 'Sport', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Unit Count': '1.0 count', 'Manufacturer Part Number': 'BENQ3-CASE', 'Model Number': 'BENQ3-CASE', 'Manufacturer': 'Amizee', 'Age Range Description': 'Adult', 'Best Sellers Rank': '4,237 in Electronics (See Top 100 in Electronics) 10 in Smartwatch Cases', 'ASIN': 'B0DLKLY2RS', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (1,683)   \n\n\n 4.1 out of 5 stars', 'Item Dimensions': '11 x 45 x 50 millimetres'}</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Apple Watch Series 10 46mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '46 Millimetres', 'Product Features': 'Heavy Duty Protection', 'Compatible Phone Models': 'Apple Watch Series 11(2025)/Series 10 46mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black', 'Pattern': 'Sports', 'Theme': 'Sport', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Unit Count': '1.0 count', 'Manufacturer Part Number': 'BENQ3-CASE', 'Model Number': 'BENQ3-CASE', 'Manufacturer': 'Amizee', 'Age Range Description': 'Adult', 'Best Sellers Rank': '4,237 in Electronics (See Top 100 in Electronics) 10 in Smartwatch Cases', 'ASIN': 'B0DLKLY2RS', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (1,683)   \n\n\n 4.1 out of 5 stars', 'Item Dimensions': '11 x 45 x 50 millimetres'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7966,60 +10099,55 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>4.5 out of 5 stars</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.5 out of 5 stars</t>
+          <t>(907)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(907)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
           <t>Compatible models: Amizee cover only compatible with Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47 mm. Note: Not suitable for other models and other types for smartwatch. Please confirm your watch size before placing an order. | 【High Quality Metal Casing】Made of high quality impact-resistant aluminum, metal and PC material. Brighten up your Samsung Galaxy Watch and ensure full protection without sacrificing beauty, and features long lasting protection against bumps. | 【Metal Bezel Protection】Raised edges around the screen provide extra protection for the Samsung Galaxy Watch screen from scratches, bumps and accidental drops. Featuring an aluminum alloy frame, you will feel sturdy from the inside. (Note: Does not include a built-in screen protector.) | 【Easy to snap on】 The snap-on design of the case is easy to install and remove. Simply press the side of the back cover case into the alignment of the crown hole. No tools, without removing the Galaxy Watch. Charge directly, without removing the case. Snap button design on the back prevents the watch from falling off. | 【What you get】1 x Blue/White Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47 mm cover. If you have any defects or quality problems of our Apple Watch cases, please feel free to contact us, our customer service will reply you within 24 hours.</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="I12" t="n">
         <v>7</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '47 Millimetres', 'Product Features': 'Kickstand, Protection for demanding use, Wireless', 'Compatible Phone Models': 'Samsung Galaxy Watch Ultra/Ultra 2(2025) 47mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Blue / white', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Manufacturer Part Number': 'GALAXYCASE-BK', 'Model Number': 'SGUltra-CASE-BUWhite', 'Manufacturer': 'Amizee', 'Best Sellers Rank': '4,485 in Electronics (See Top 100 in Electronics) 11 in Smartwatch Cases', 'ASIN': 'B0GCHZ4RP5', 'Customer Reviews': '4.5  4.5 out of 5 stars   \n    (907)   \n\n\n 4.5 out of 5 stars', 'Item Dimensions': '48 x 46 x 16 millimetres', 'Item Weight': '0.47 Ounces'}</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '47 Millimetres', 'Product Features': 'Kickstand, Protection for demanding use, Wireless', 'Compatible Phone Models': 'Samsung Galaxy Watch Ultra/Ultra 2(2025) 47mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Blue / white', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Manufacturer Part Number': 'GALAXYCASE-BK', 'Model Number': 'SGUltra-CASE-BUWhite', 'Manufacturer': 'Amizee', 'Best Sellers Rank': '4,485 in Electronics (See Top 100 in Electronics) 11 in Smartwatch Cases', 'ASIN': 'B0GCHZ4RP5', 'Customer Reviews': '4.5  4.5 out of 5 stars   \n    (907)   \n\n\n 4.5 out of 5 stars', 'Item Dimensions': '48 x 46 x 16 millimetres', 'Item Weight': '0.47 Ounces'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8044,60 +10172,55 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>4.3 out of 5 stars</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.3 out of 5 stars</t>
+          <t>(361)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(361)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
           <t>[Applicable Model]---- Compatible with Huawei Watch GT 5 46mm (Not for Huawei Watch GT 5 41mm). This case is designed with precise cutouts for functional buttons, speaker hole, charging hole, etc.(The package only contains cases, watch and watch band are not included!) | [Full Protection] --- Our case covers the full front and curved edges of the watch, provides complete protection of your watch against dust, fingerprints, scratches, drops or bumps to the ground. | [Sensitive Touch and High Transparency]---- Made of premium TPU material, smooth, transparent and without influencing touch sensitivity. Gives you original touch sensitivity and high touch responsiveness. Hydrophobic and oleophobic screen coating can easily separate oil, fingerprints and other stains, make the screen easy to clean, prevent your watch screens from looking shabby and dull. | [Ultra Slim and Easy to Install] ---- Ultra thin and lightweight, never be a burden on your wrist from your work to your workout. Easy to wear and remove and designed to be compatible with the charger, you don't need to remove the protective case when charging. | [What you get] --- 3 x iVoler cases with built-in screen protector (2 transparent + 1 black). [Warm Tip]: Using this product in the gym or during sports activities may cause moisture (sweating) to build up between this product and the monitor screen. Use dry cloth to keep it dry if you have water, if you have any questions or product problems, please contact us, we will do the best service for you.</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="I13" t="n">
         <v>7</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'huawei watch gt 5 46mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'huawei watch gt 5 46mm', 'Special Features': 'Rounded Edge, Shockproof', 'Screen Size': '46 Millimetres', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Compatible Wearable Computer Models': 'Huawei WATCH GT, SUUNTO 5', 'Unit Count': '3.0 count', 'Number of Items': '3', 'Brand Name': 'ivoler', 'Model Name': 'iVoler Huawei Watch GT 5 46mm Screen Protector', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00039', 'Best Sellers Rank': '3,967 in Electronics (See Top 100 in Electronics) 12 in Smartwatch Cases', 'ASIN': 'B0DJTDNSQN', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (361)   \n\n\n 4.3 out of 5 stars', 'Material': 'Silicone'}</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'huawei watch gt 5 46mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'huawei watch gt 5 46mm', 'Special Features': 'Rounded Edge, Shockproof', 'Screen Size': '46 Millimetres', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Compatible Wearable Computer Models': 'Huawei WATCH GT, SUUNTO 5', 'Unit Count': '3.0 count', 'Number of Items': '3', 'Brand Name': 'ivoler', 'Model Name': 'iVoler Huawei Watch GT 5 46mm Screen Protector', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00039', 'Best Sellers Rank': '3,967 in Electronics (See Top 100 in Electronics) 12 in Smartwatch Cases', 'ASIN': 'B0DJTDNSQN', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (361)   \n\n\n 4.3 out of 5 stars', 'Material': 'Silicone'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8122,60 +10245,55 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>4.1 out of 5 stars</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.1 out of 5 stars</t>
+          <t>(3,036)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(3,036)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
           <t>【Compatible Models】Designed for Apple Watch SE 3/2/1 Series 6/5/4 40mm. NOTE: Not suitable for other models and other types of smartwatch. Please confirm your watch size before placing an order. | 【Full Body Protection】Made of high quality hard PC material, with built-in screen protector. 2 in 1 design provides robust 360 degree protection. Full body protection keeps your Apple Watch 40mm from scratches and drops. | High sensitivity touch: The high-transparency tempered glass screen protector provides original vision and touch experience; Ultra-thin, three-dimensional right-angle edge, the design is slimmer. | 【Precise Fit】Sensitive button covers allow responsive pressing; Easy access to Apple Watch button and functions with precise cutouts; Easy to install, charge directly, without removing the case. | 【WHAT YOU GET】2 x Black Apple Watch Case 40 mm; We offer a one-year warranty, please feel free to contact us for any problem, a satisfactory solution is promised forever.</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="I14" t="n">
         <v>6</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Apple Watch Series 6/5/4/SE 40mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'Apple Watch', 'Special Features': 'Robust protection, Scratch Resistant, Shockproof, screen protector', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Waterproof', 'Screen Size': '44 Millimetres', 'Screen Surface Description': 'Matte', 'Clarity': '0.99', 'Compatible Wearable Computer Models': 'Apple Watch SE 40mm', 'Item Dimensions L x W': '43L x 38W millimetres', 'Unit Count': '1.0 unité', 'Number of Items': '2', 'Brand Name': 'Amizee', 'Model Number': 'APPLECASE-ZB', 'Model Name': 'CAZB-40-BLC', 'Colour': 'Black / Black', 'Manufacturer': 'Amizee', 'Part Number': 'CAZB-40-BLC', 'Item Weight': '0.18 Ounces', 'Included Components': 'Case for Apple Watch 40mm', 'Best Sellers Rank': '3,327 in Electronics (See Top 100 in Electronics) 13 in Smartwatch Cases 92 in Smartwatch Screen Protectors &amp; Foils', 'ASIN': 'B0C2CM7QWR', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (3,036)   \n\n\n 4.1 out of 5 stars', 'Material': 'Polycarbonate, Tempered Glass'}</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Apple Watch Series 6/5/4/SE 40mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'Apple Watch', 'Special Features': 'Robust protection, Scratch Resistant, Shockproof, screen protector', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Waterproof', 'Screen Size': '44 Millimetres', 'Screen Surface Description': 'Matte', 'Clarity': '0.99', 'Compatible Wearable Computer Models': 'Apple Watch SE 40mm', 'Item Dimensions L x W': '43L x 38W millimetres', 'Unit Count': '1.0 unité', 'Number of Items': '2', 'Brand Name': 'Amizee', 'Model Number': 'APPLECASE-ZB', 'Model Name': 'CAZB-40-BLC', 'Colour': 'Black / Black', 'Manufacturer': 'Amizee', 'Part Number': 'CAZB-40-BLC', 'Item Weight': '0.18 Ounces', 'Included Components': 'Case for Apple Watch 40mm', 'Best Sellers Rank': '3,327 in Electronics (See Top 100 in Electronics) 13 in Smartwatch Cases 92 in Smartwatch Screen Protectors &amp; Foils', 'ASIN': 'B0C2CM7QWR', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (3,036)   \n\n\n 4.1 out of 5 stars', 'Material': 'Polycarbonate, Tempered Glass'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N14" t="n">
+      <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8200,60 +10318,55 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>4.2 out of 5 stars</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.2 out of 5 stars</t>
+          <t>(540)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(540)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
           <t>1. Compatible models: Only compatible with Xiaomi Redmi Watch 5 Active, please confirm your watch model before purchasing. 4 colours per pack: transparent, black, pink, blue. | 2. Full protection: It protects the watch screen and sides from scratches, scrapes, chips, collisions or other damage. | 3. Material: durable PC case with screen protector. No influence on touch sensitivity, sensor functions work well with watch case. | 4. Easy to install: its snap-on design to avoid peeling off. Precise hole cutouts make it easy to access all buttons or buttons, slim and lightweight, no need to remove the watch case when charging. | 5. Tips: Recommended for removing the case when swimming or bathing. Moisture can be trapped in case when you exercise, please use the microfiber cloth to wipe it.</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="I15" t="n">
         <v>5</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Xiaomi Redmi Watch 5 Active', 'Special Features': 'High quality tempered glass', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Not Water Resistant', 'Screen Surface Description': 'Glossy', 'Clarity': '10', 'Unit Count': '4.0 count', 'Number of Items': '4', 'Material': 'Polycarbonate', 'Brand Name': 'Bigqin', 'Model Number': '13XMRMW5A-4PC', 'Model Name': 'Xiaomi Redmi Watch 5 Active Screen Protector 4-Pack', 'Customer Package Type': 'FFP Packaging', 'Colour': 'Redmi Watch 5 Active', 'Manufacturer': 'Bigqin', 'Part Number': 'B02', 'Included Components': 'Watch', 'Best Sellers Rank': '4,821 in Electronics (See Top 100 in Electronics) 14 in Smartwatch Cases', 'ASIN': 'B0DM4WJ7XH', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (540)   \n\n\n 4.2 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Xiaomi Redmi Watch 5 Active', 'Special Features': 'High quality tempered glass', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Not Water Resistant', 'Screen Surface Description': 'Glossy', 'Clarity': '10', 'Unit Count': '4.0 count', 'Number of Items': '4', 'Material': 'Polycarbonate', 'Brand Name': 'Bigqin', 'Model Number': '13XMRMW5A-4PC', 'Model Name': 'Xiaomi Redmi Watch 5 Active Screen Protector 4-Pack', 'Customer Package Type': 'FFP Packaging', 'Colour': 'Redmi Watch 5 Active', 'Manufacturer': 'Bigqin', 'Part Number': 'B02', 'Included Components': 'Watch', 'Best Sellers Rank': '4,821 in Electronics (See Top 100 in Electronics) 14 in Smartwatch Cases', 'ASIN': 'B0DM4WJ7XH', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (540)   \n\n\n 4.2 out of 5 stars'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8278,60 +10391,55 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>4.3 out of 5 stars</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.3 out of 5 stars</t>
+          <t>(90)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(90)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
           <t>[Applicable Model]---- Compatible with Amazfit Active 2 (Round Edition) (Not for Amazfit Active 2 Square Edition). This case is designed with precise cutouts for functional buttons, speaker hole, charging hole, etc.(The package only contains cases, watch and watch band are not included!) | [Full Protection] --- Our case covers the full front and curved edges of the watch, provides complete protection of your watch against dust, fingerprints, scratches, drops or bumps to the ground. | [Sensitive Touch and High Transparency]---- Made of premium TPU material, smooth, transparent and without influencing touch sensitivity. Gives you original touch sensitivity and high touch responsiveness. Hydrophobic and oleophobic screen coating can easily separate oil, fingerprints and other stains, make the screen easy to clean, prevent your watch screens from looking shabby and dull. | [Ultra Slim and Easy to Install] ---- Ultra thin and lightweight, never be a burden on your wrist from your work to your workout. Easy to wear and remove and designed to be compatible with the charger, you don't need to remove the protective case when charging. | [What you get] --- 3 x iVoler cases with built-in screen protector (2 transparent + 1 black). [Warm Tip]: Using this product in the gym or during sports activities may cause moisture (sweating) to build up between this product and the monitor screen. Use dry cloth to keep it dry if you have water, if you have any questions or product problems, please contact us, we will do the best service for you.</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="I16" t="n">
         <v>7</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active 2 (Round Edition)', 'Special Features': 'Rounded Edge, Shockproof', 'Finish Type': 'Glossy', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Item Dimensions L x W': '7.2L x 8.2W centimetres', 'Unit Count': '1.0 unité', 'Number of Items': '3', 'Material': 'Silicone', 'Brand Name': 'ivoler', 'Model Name': 'Amazfit Active 2 (Round Edition) Screen Protector', 'Colour': '2 Transparent + 1 Black', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00073', 'Product Warranty': '1', 'Included Components': 'Case', 'Best Sellers Rank': '4,873 in Electronics (See Top 100 in Electronics) 15 in Smartwatch Cases', 'ASIN': 'B0DSW4V65Z', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (90)   \n\n\n 4.3 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active 2 (Round Edition)', 'Special Features': 'Rounded Edge, Shockproof', 'Finish Type': 'Glossy', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Item Dimensions L x W': '7.2L x 8.2W centimetres', 'Unit Count': '1.0 unité', 'Number of Items': '3', 'Material': 'Silicone', 'Brand Name': 'ivoler', 'Model Name': 'Amazfit Active 2 (Round Edition) Screen Protector', 'Colour': '2 Transparent + 1 Black', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00073', 'Product Warranty': '1', 'Included Components': 'Case', 'Best Sellers Rank': '4,873 in Electronics (See Top 100 in Electronics) 15 in Smartwatch Cases', 'ASIN': 'B0DSW4V65Z', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (90)   \n\n\n 4.3 out of 5 stars'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8356,54 +10464,49 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
         <v>1</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8428,54 +10531,49 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
         <v>1</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8500,54 +10598,49 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
         <v>1</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8572,54 +10665,49 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
         <v>1</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8644,54 +10732,49 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8716,54 +10799,49 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
         <v>1</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8788,54 +10866,49 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
         <v>1</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N23" t="n">
+      <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8860,54 +10933,49 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
         <v>1</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N24" t="n">
+      <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8932,54 +11000,49 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="n">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
         <v>1</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N25" t="n">
+      <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9004,54 +11067,49 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
           <t>Pas de note</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
         <v>1</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N26" t="n">
+      <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9076,70 +11134,65 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="G27" t="n">
         <v>5105</v>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
         <v>7</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="M27" t="n">
         <v>0</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>[Compatibility] Perfectly compatible with Apple Watch Ultra 49mm. (This case does not come with a screen protector)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>[Compatibility] Perfectly compatible with Apple Watch Ultra 49mm. (This case does not come with a screen protector)</t>
+          <t>[TPU Material] This shockproof TPU case is soft, flexible and durable and provides long-lasting impact protection you can rely on.</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>[TPU Material] This shockproof TPU case is soft, flexible and durable and provides long-lasting impact protection you can rely on.</t>
+          <t>[Easy to Put on and Remove] This Apple Watch Ultra 49mm case is equipped with precise cutouts that allow easy access to all controls, buttons, sensors and watch functions. Does not interfere with bezel rotation and other watch functions, easy to put on and take off, this case does not need to be removed when charging.</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>[Easy to Put on and Remove] This Apple Watch Ultra 49mm case is equipped with precise cutouts that allow easy access to all controls, buttons, sensors and watch functions. Does not interfere with bezel rotation and other watch functions, easy to put on and take off, this case does not need to be removed when charging.</t>
+          <t>[PC Keys Design] Comes with PC button, allows you to use more easily. Precise cut, easy access to all controls, buttons, sensors and functions.</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
-        <is>
-          <t>[PC Keys Design] Comes with PC button, allows you to use more easily. Precise cut, easy access to all controls, buttons, sensors and functions.</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
         <is>
           <t>[No Screen Protector] The Apple Watch 49mm protective case is not equipped with a protective film. Supports use with other screen protectors.</t>
         </is>
@@ -9168,70 +11221,65 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="G28" t="n">
         <v>98</v>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
         <v>7</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Xiaomi Smart Band 10', 'Form Factor': 'Cover', 'Product Features': 'Kratzfest', 'Compatible Phone Models': 'Xiaomi Smart Band 10', 'Colour': 'Black&amp;Black&amp;Black', 'Shell Type': 'Soft', 'Enclosure Material': 'Thermoplastic Polyurethane', 'Brand Name': 'Diruite', 'Unit Count': '3.0 count', 'Manufacturer': 'Diruite', 'Best Sellers Rank': '5,917 in Electronics (See Top 100 in Electronics) 27 in Smartwatch Cases', 'ASIN': 'B0FFYWVP45', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (98)   \n\n\n 4.4 out of 5 stars', 'Item Weight': '20 Grams'}</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Xiaomi Smart Band 10', 'Form Factor': 'Cover', 'Product Features': 'Kratzfest', 'Compatible Phone Models': 'Xiaomi Smart Band 10', 'Colour': 'Black&amp;Black&amp;Black', 'Shell Type': 'Soft', 'Enclosure Material': 'Thermoplastic Polyurethane', 'Brand Name': 'Diruite', 'Unit Count': '3.0 count', 'Manufacturer': 'Diruite', 'Best Sellers Rank': '5,917 in Electronics (See Top 100 in Electronics) 27 in Smartwatch Cases', 'ASIN': 'B0FFYWVP45', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (98)   \n\n\n 4.4 out of 5 stars', 'Item Weight': '20 Grams'}</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="M28" t="n">
         <v>0</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>Compatible models: this soft TPU case is specially designed screen protector for Xiaomi Smart Band 10 and offers full protection without slots. Ultra soft texture effectively protects your watch from scratches, bumps and drops.</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Compatible models: this soft TPU case is specially designed screen protector for Xiaomi Smart Band 10 and offers full protection without slots. Ultra soft texture effectively protects your watch from scratches, bumps and drops.</t>
+          <t>High fit: The soft case cover precisely fits the Xiaomi Smart Band 10 perfectly without compromising the normal operation and operation of the watch, while providing a comfortable feel.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>High fit: The soft case cover precisely fits the Xiaomi Smart Band 10 perfectly without compromising the normal operation and operation of the watch, while providing a comfortable feel.</t>
+          <t>Shock and drop resistance: The elasticity and cushioning of the TPU material provide effective protection against internal damage when your Xiaomi Smart Band 10 is touched.</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Shock and drop resistance: The elasticity and cushioning of the TPU material provide effective protection against internal damage when your Xiaomi Smart Band 10 is touched.</t>
+          <t>High sensitivity touch control: The Xiaomi Smart Band 10 watch protective case is equipped with a high-resolution screen protector that does not affect the usability of the screen and maintains the touch sensitivity of the watch and monitor, presenting crisp and original image quality and original touch sensitivity.</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
-        <is>
-          <t>High sensitivity touch control: The Xiaomi Smart Band 10 watch protective case is equipped with a high-resolution screen protector that does not affect the usability of the screen and maintains the touch sensitivity of the watch and monitor, presenting crisp and original image quality and original touch sensitivity.</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
         <is>
           <t>Easy installation: precisely matches all the holes in the watch of your Xiaomi Smart Band 10. Screen Protectors for Xiaomi Smart Band 10*3</t>
         </is>
@@ -9260,70 +11308,65 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="G29" t="n">
         <v>32</v>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
         <v>7</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Amazfit Active Max', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active Max', 'Special Features': '9 H Surface Hardness', 'Screen Surface Description': 'Hard', 'Clarity': '9', 'Compatible Wearable Computer Models': 'Amazfit Active', 'Unit Count': '2.0 count', 'Number of Items': '2', 'Material': 'Plastic Glass', 'Brand Name': 'GIOPUEY', 'Model Number': 'GIOPUEY', 'Colour': '2 x black', 'Manufacturer': 'GIOPUEY', 'Part Number': 'Amazfit Active Max', 'Item Weight': '10 Grams', 'Best Sellers Rank': '5,952 in Electronics (See Top 100 in Electronics) 28 in Smartwatch Cases', 'ASIN': 'B0G6C44RPY', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (32)   \n\n\n 4.1 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Amazfit Active Max', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active Max', 'Special Features': '9 H Surface Hardness', 'Screen Surface Description': 'Hard', 'Clarity': '9', 'Compatible Wearable Computer Models': 'Amazfit Active', 'Unit Count': '2.0 count', 'Number of Items': '2', 'Material': 'Plastic Glass', 'Brand Name': 'GIOPUEY', 'Model Number': 'GIOPUEY', 'Colour': '2 x black', 'Manufacturer': 'GIOPUEY', 'Part Number': 'Amazfit Active Max', 'Item Weight': '10 Grams', 'Best Sellers Rank': '5,952 in Electronics (See Top 100 in Electronics) 28 in Smartwatch Cases', 'ASIN': 'B0G6C44RPY', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (32)   \n\n\n 4.1 out of 5 stars'}</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="M29" t="n">
         <v>0</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>Easy to install: you can install the housing easily. It does not affect the load after installation.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Easy to install: you can install the housing easily. It does not affect the load after installation.</t>
+          <t>Material: hard plastic + tempered glass</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Material: hard plastic + tempered glass</t>
+          <t>Anti-Scratch The protective case with built-in 9H tempered glass can effectively protect your watch from daily scratches and bumps.</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Anti-Scratch The protective case with built-in 9H tempered glass can effectively protect your watch from daily scratches and bumps.</t>
+          <t>TOUCH SENSITIVE - Ultra thin tempered glass screen protector retains the original sensitive touch of the watch and ensures a quick launch of the app.</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
-        <is>
-          <t>TOUCH SENSITIVE - Ultra thin tempered glass screen protector retains the original sensitive touch of the watch and ensures a quick launch of the app.</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
         <is>
           <t>Access to all functions: Direct charging without removing the case and strap. Precise cutouts for easy access to all function buttons.</t>
         </is>
@@ -9352,70 +11395,65 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="G30" t="n">
         <v>68</v>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
         <v>7</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Garmin Vivoactive 6', 'Form Factor': 'Case', 'Product Features': 'Scratch Resistant, Shockproof', 'Compatible Phone Models': 'Garmin Vivoactive 6', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Clear*3', 'Shell Type': 'Hard', 'Enclosure Material': 'Tempered Glass', 'Brand Name': 'Kamita', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '6,152 in Electronics (See Top 100 in Electronics) 29 in Smartwatch Cases', 'ASIN': 'B0F6LP1M79', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (68)   \n\n\n 4.2 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Garmin Vivoactive 6', 'Form Factor': 'Case', 'Product Features': 'Scratch Resistant, Shockproof', 'Compatible Phone Models': 'Garmin Vivoactive 6', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Clear*3', 'Shell Type': 'Hard', 'Enclosure Material': 'Tempered Glass', 'Brand Name': 'Kamita', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '6,152 in Electronics (See Top 100 in Electronics) 29 in Smartwatch Cases', 'ASIN': 'B0F6LP1M79', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (68)   \n\n\n 4.2 out of 5 stars'}</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="M30" t="n">
         <v>0</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>COMPATIBILITY: This specially designed Kamita protective case is compatible with Garmin Vivoactive 6, which can provide full protection for your watch. The screen protectors and protective case fit your watch perfectly. NOTE: This case does not fit other watch models. Please check the model of your watch before purchasing.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>COMPATIBILITY: This specially designed Kamita protective case is compatible with Garmin Vivoactive 6, which can provide full protection for your watch. The screen protectors and protective case fit your watch perfectly. NOTE: This case does not fit other watch models. Please check the model of your watch before purchasing.</t>
+          <t>New material: This case compatible with Garmin Vivoactive 6 is made of hard and durable PC, which is more resistant to wear and does not lose its colors. The smooth surface ensures smooth gliding and tactile sensitivity, which gives you a better touch feeling.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>New material: This case compatible with Garmin Vivoactive 6 is made of hard and durable PC, which is more resistant to wear and does not lose its colors. The smooth surface ensures smooth gliding and tactile sensitivity, which gives you a better touch feeling.</t>
+          <t>Total protection: our Garmin Vivo Active 6 hard PC cases can cover all sides of your watch, ensuring total protection for your watch. Shockproof and scratch resistant design protects the watch from bumps and scratches.</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Total protection: our Garmin Vivo Active 6 hard PC cases can cover all sides of your watch, ensuring total protection for your watch. Shockproof and scratch resistant design protects the watch from bumps and scratches.</t>
+          <t>Precise cutouts and easy installation: Our watch cover has a precise button cut-out that allows it to snap into place quickly and fit your watch precisely. Allows easy access to all buttons, sound holes, sensors and smartwatch functions. What's more, the snap-on design is easy to install and remove without any tools. It is also not necessary to remove the case to charge.</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
-        <is>
-          <t>Precise cutouts and easy installation: Our watch cover has a precise button cut-out that allows it to snap into place quickly and fit your watch precisely. Allows easy access to all buttons, sound holes, sensors and smartwatch functions. What's more, the snap-on design is easy to install and remove without any tools. It is also not necessary to remove the case to charge.</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
         <is>
           <t>Package includes: The package includes 3 pieces of covers for Garmin Vivo Active 6. Humanized ergonomic house, air cushion technology to protect all areas. Suitable for men, women, girls, boys and any occasion.</t>
         </is>
@@ -9444,70 +11482,65 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="G31" t="n">
         <v>74</v>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
         <v>6</v>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Garmin Venu 4 45mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '45 Millimetres', 'Compatible Phone Models': 'Garmin Venu 4 45mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black x 2', 'Shell Type': 'Soft', 'Enclosure Material': 'Silicone', 'Item Dimensions': '2 x 2 x 2 millimetres', 'Item Weight': '10 Grams', 'Brand Name': 'GIOPUEY', 'Unit Count': '2.0 count', 'Manufacturer Part Number': 'Garmin Venu 4 45mm', 'Model Number': 'GIOPUEY', 'Manufacturer': 'GIOPUEY', 'Best Sellers Rank': '6,206 in Electronics (See Top 100 in Electronics) 30 in Smartwatch Cases', 'ASIN': 'B0GDJSFDL4', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (74)   \n\n\n 4.4 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Garmin Venu 4 45mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '45 Millimetres', 'Compatible Phone Models': 'Garmin Venu 4 45mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black x 2', 'Shell Type': 'Soft', 'Enclosure Material': 'Silicone', 'Item Dimensions': '2 x 2 x 2 millimetres', 'Item Weight': '10 Grams', 'Brand Name': 'GIOPUEY', 'Unit Count': '2.0 count', 'Manufacturer Part Number': 'Garmin Venu 4 45mm', 'Model Number': 'GIOPUEY', 'Manufacturer': 'GIOPUEY', 'Best Sellers Rank': '6,206 in Electronics (See Top 100 in Electronics) 30 in Smartwatch Cases', 'ASIN': 'B0GDJSFDL4', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (74)   \n\n\n 4.4 out of 5 stars'}</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="M31" t="n">
         <v>0</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>Package includes: 2 x Silicone Protective Case</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Package includes: 2 x Silicone Protective Case</t>
+          <t>NO INTERFERENCE WITH SCREEN - The semi-wrap design leaves the screen fully exposed and does not interfere with the touch operation of the watch or the screen display, allowing you to use the features of the anywhere, anytime.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>NO INTERFERENCE WITH SCREEN - The semi-wrap design leaves the screen fully exposed and does not interfere with the touch operation of the watch or the screen display, allowing you to use the features of the anywhere, anytime.</t>
+          <t>Perfect Fit: Precise cutting and fitting technology ensures that the case fits your perfectly without interfering with the watch's operation, charging and wearing, allowing you to enjoy a comfortable and pleasant using experience.</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Perfect Fit: Precise cutting and fitting technology ensures that the case fits your perfectly without interfering with the watch's operation, charging and wearing, allowing you to enjoy a comfortable and pleasant using experience.</t>
+          <t>One-Step Installation: Thanks to the one-step installation design, there is no need for tools or complicated steps, just gently slip on the case to complete the installation.</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
-        <is>
-          <t>One-Step Installation: Thanks to the one-step installation design, there is no need for tools or complicated steps, just gently slip on the case to complete the installation.</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
         <is>
           <t>QUALITY SERVICE: If you have any questions or needs, please feel free to contact our customer service team, we will try our best to solve your problems and ensure your satisfaction.</t>
         </is>
@@ -9526,38 +11559,59 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9572,38 +11626,59 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9618,38 +11693,59 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9664,38 +11760,59 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Aucune description</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Pas de note</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Non trouvé</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Aucune déclinaison</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9720,14 +11837,10 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -9741,7 +11854,6 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9766,14 +11878,10 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -9787,7 +11895,6 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9812,14 +11919,10 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -9833,7 +11936,6 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9858,14 +11960,10 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -9879,7 +11977,6 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9904,14 +12001,10 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -9925,7 +12018,6 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9950,14 +12042,10 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -9971,7 +12059,6 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9996,14 +12083,10 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -10017,7 +12100,6 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -10042,14 +12124,10 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -10063,7 +12141,6 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -10088,14 +12165,10 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -10109,7 +12182,6 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -10134,14 +12206,10 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -10155,7 +12223,6 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -10180,14 +12247,10 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -10201,7 +12264,6 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -10226,14 +12288,10 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -10247,7 +12305,6 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -10272,14 +12329,10 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -10293,7 +12346,6 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -10318,14 +12370,10 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -10339,7 +12387,6 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -10364,14 +12411,10 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -10385,7 +12428,6 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10410,14 +12452,10 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -10431,7 +12469,6 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -9262,7 +9262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S51"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9303,60 +9303,55 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bullet_Points</t>
+          <t>Nombre_Images</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Nombre_Images</t>
+          <t>Caracteristiques</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Caracteristiques</t>
+          <t>BSR_Categories</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>BSR_Categories</t>
+          <t>Declinaisons</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Declinaisons</t>
+          <t>Nb_Declinaisons</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Nb_Declinaisons</t>
+          <t>Date_Analyse</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Date_Analyse</t>
+          <t>Bullet_1</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Bullet_1</t>
+          <t>Bullet_2</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Bullet_2</t>
+          <t>Bullet_3</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Bullet_3</t>
+          <t>Bullet_4</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Bullet_4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Bullet_5</t>
         </is>
@@ -9396,42 +9391,37 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9467,42 +9457,37 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3" t="n">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9538,42 +9523,37 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4" t="n">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9609,42 +9589,37 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9680,42 +9655,37 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="H6" t="n">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9751,42 +9721,37 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Aucun</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="H7" t="n">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9824,42 +9789,37 @@
           <t>(2,040)</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>【COMPATIBILITY】Tensea iWatch screen protector with back cover is designed to fit Apple Watch Ultra 3 49mm, Apple Watch Ultra 2 49mm and Apple Watch Ultra 49mm. The bumper cover built into the screen protector provides a perfect fit. | 【Daily Water Resistance】 Apple Watch Ultra 3/Ultra 2/Ultra 49mm has a built-in seal that effectively prevents water from entering the screen. Its exceptional water resistance for everyday use makes it possible to use it with confidence during activities such as showering, hand washing, sweating or showering. [Note: Not suitable for deep water environments such as diving or swimming.] | 【360°Protection】This protective case, compatible with the surface of iWatch Ultra 3/Ultra 2/Ultra 49mm, provides full protection to the front and back of your watch, effectively resisting dust, dirt, scratches and damage. The 9H tempered glass screen protector preserves touch sensitivity, while the sweat-resistant case design allows for easy installation without having to remove the band. | 【Upgraded Materials】 Scratch-resistant and impact-resistant tempered glass has a hardness of 9H. Shock absorbing polycarbonate provides superior rigidity, improved resilience and better protection compared to conventional TPU. Glass construction prevents fogging caused by temperature fluctuations. | 【Easy Installation】The product page includes installation video and the package contains installation instructions. A removal tool is provided to allow the watch case to be removed without damaging it.</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="H8" t="n">
         <v>7</v>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique trouvée</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Aucune caractéristique trouvée</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9893,42 +9853,37 @@
           <t>(61)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Compatible Model: Compatible with Garmin Forerunner 165 / 165 Music. Precise design will fit your watch perfectly. (Note: Please check your watch model number before purchasing) | Full protection: The protective case for Garmin Forerunner 165 / 165 Music offers full screen protection from four sides to the corners. Slightly higher edges protect the surface of your watch and protect it from scratches, bumps and accidental drops. | Effective protective TPU material: made of high-quality and scratch-resistant TPU material. Soft and lightweight, very comfortable to wear, leaves no air bubbles between the case and the screen, giving you an original viewing experience and touch experience. | Easy to install: no tools required. You don't need to remove the case, just align the holes with the watch buttons and put the case in place. Precise cutouts for quick access to screen, button and sensor. The case does not need to be removed when charging. | Fashion and Light: Soft and thin TPU materials make it easy to put on and take off your watch. Slim and lightweight, never strain your wrist from work to exercise. Give you a better user experience.</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="H9" t="n">
         <v>7</v>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'GM 165', 'Compatible Phone Models': 'Garmin Forerunner 165, Garmin Forerunner 165 Music', 'Special Features': 'Effective protective TPU material, full protection', 'Clarity': '10', 'Compatible Wearable Computer Models': 'Garmin Forerunner 165', 'Item Dimensions L x W': '10L x 6W centimetres', 'Unit Count': '2.0 unité', 'Number of Items': '2', 'Material': 'Silicone', 'Brand Name': 'TUTUO', 'Model Number': 'GM 165-HS+TM', 'Model Name': 'GM 165-HS+TM', 'Colour': 'Transparent/Green', 'Manufacturer': 'TUTUO', 'Part Number': 'GM 165-HS+TM', 'Best Sellers Rank': '4,130 in Electronics (See Top 100 in Electronics) 8 in Smartwatch Cases', 'ASIN': 'B0GHNJ6ZY3', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (61)   \n\n\n 4.4 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'GM 165', 'Compatible Phone Models': 'Garmin Forerunner 165, Garmin Forerunner 165 Music', 'Special Features': 'Effective protective TPU material, full protection', 'Clarity': '10', 'Compatible Wearable Computer Models': 'Garmin Forerunner 165', 'Item Dimensions L x W': '10L x 6W centimetres', 'Unit Count': '2.0 unité', 'Number of Items': '2', 'Material': 'Silicone', 'Brand Name': 'TUTUO', 'Model Number': 'GM 165-HS+TM', 'Model Name': 'GM 165-HS+TM', 'Colour': 'Transparent/Green', 'Manufacturer': 'TUTUO', 'Part Number': 'GM 165-HS+TM', 'Best Sellers Rank': '4,130 in Electronics (See Top 100 in Electronics) 8 in Smartwatch Cases', 'ASIN': 'B0GHNJ6ZY3', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (61)   \n\n\n 4.4 out of 5 stars'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9966,42 +9921,37 @@
           <t>(192)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>COMPATIBILITY: This specially designed Kamita protective case is compatible with Garmin Vivoactive 5, which can provide full protection for your watch. The screen protectors and protective case fit your watch perfectly. NOTE: This case does not fit other watch models. Please check the model of your watch before purchasing. | New material: This case compatible with Garmin Vivoactive 5 is made of hard and durable PC, which is more resistant to wear and does not lose its colors. The smooth surface ensures smooth gliding and tactile sensitivity, which gives you a better touch feeling. | Total protection: our Garmin Vivo Active 5 hard PC cases can cover all sides of your watch, ensuring total protection for your watch. Shockproof and scratch resistant design protects the watch from bumps and scratches. | Precise cutouts and easy installation: Our watch cover has a precise button cut-out that allows it to snap into place quickly and fit your watch precisely. Allows easy access to all buttons, sound holes, sensors and smartwatch functions. What's more, the snap-on design is easy to install and remove without any tools. It is also not necessary to remove the case to charge. | Package includes: The package includes 3 pieces of covers for Garmin Vivo Active 5. Humanized ergonomic house, air cushion technology to protect all areas. Suitable for men, women, girls, boys and any occasion.</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="H10" t="n">
         <v>7</v>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatches', 'Form Factor': 'Case', 'Product Features': 'Shock and scratch resistant', 'Compatible Phone Models': 'Garmin Vivoactive 5', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Transparent+Pink+White', 'Shell Type': 'Hard', 'Enclosure Material': 'Polycarbonate', 'Brand Name': 'Kamita', 'Unit Count': '3.0 count', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '4,168 in Electronics (See Top 100 in Electronics) 9 in Smartwatch Cases', 'ASIN': 'B0DSZLRYTB', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (192)   \n\n\n 4.2 out of 5 stars', 'Item Dimensions': '8 x 1 x 1.3 centimetres'}</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Smartwatches', 'Form Factor': 'Case', 'Product Features': 'Shock and scratch resistant', 'Compatible Phone Models': 'Garmin Vivoactive 5', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Transparent+Pink+White', 'Shell Type': 'Hard', 'Enclosure Material': 'Polycarbonate', 'Brand Name': 'Kamita', 'Unit Count': '3.0 count', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '4,168 in Electronics (See Top 100 in Electronics) 9 in Smartwatch Cases', 'ASIN': 'B0DSZLRYTB', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (192)   \n\n\n 4.2 out of 5 stars', 'Item Dimensions': '8 x 1 x 1.3 centimetres'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10039,42 +9989,37 @@
           <t>(1,683)</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>【Compatible Models】Amizee cover only compatible with Apple Watch Series 11 (2025)/Series 10 46mm Cover. Note: Not suitable for other models and other types for smartwatch. Please confirm your watch size before placing an order. | 【Ultra 3/2/1 Second Change】Simple and tool-free installation transforms the appearance of your watch in seconds, allowing you to enjoy the Ultra 3/2/1 wearing experience, providing a stylish yet functional design and giving you a personal experience. The right button of the case has an updated built-in watch crown cover. (Note: crown does not work for ECG) | 【High quality metal casing】Made of high quality shockproof metal aluminum. Brighten up your Apple Watch and provide full protection without sacrificing beauty, and has long lasting protection against shocks. The snap-on design of the case is easy to install and remove. Charge directly, without removing the case. | 【Metal Bezel Protection】Raised edges around the screen for extra protection of the Apple Watch screen from scratches, bumps and accidental drops. Featuring an aluminum alloy frame, you will feel sturdy from the inside. (Note: does not include the built-in screen protector) | 【What you get】1 x black apple watch case 46 mm. If you have any defects or quality problems of our Apple Watch cases, please feel free to contact us, our customer service will reply you within 24 hours.</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="H11" t="n">
         <v>6</v>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Apple Watch Series 10 46mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '46 Millimetres', 'Product Features': 'Heavy Duty Protection', 'Compatible Phone Models': 'Apple Watch Series 11(2025)/Series 10 46mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black', 'Pattern': 'Sports', 'Theme': 'Sport', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Unit Count': '1.0 count', 'Manufacturer Part Number': 'BENQ3-CASE', 'Model Number': 'BENQ3-CASE', 'Manufacturer': 'Amizee', 'Age Range Description': 'Adult', 'Best Sellers Rank': '4,237 in Electronics (See Top 100 in Electronics) 10 in Smartwatch Cases', 'ASIN': 'B0DLKLY2RS', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (1,683)   \n\n\n 4.1 out of 5 stars', 'Item Dimensions': '11 x 45 x 50 millimetres'}</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Apple Watch Series 10 46mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '46 Millimetres', 'Product Features': 'Heavy Duty Protection', 'Compatible Phone Models': 'Apple Watch Series 11(2025)/Series 10 46mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black', 'Pattern': 'Sports', 'Theme': 'Sport', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Unit Count': '1.0 count', 'Manufacturer Part Number': 'BENQ3-CASE', 'Model Number': 'BENQ3-CASE', 'Manufacturer': 'Amizee', 'Age Range Description': 'Adult', 'Best Sellers Rank': '4,237 in Electronics (See Top 100 in Electronics) 10 in Smartwatch Cases', 'ASIN': 'B0DLKLY2RS', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (1,683)   \n\n\n 4.1 out of 5 stars', 'Item Dimensions': '11 x 45 x 50 millimetres'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10112,42 +10057,37 @@
           <t>(907)</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Compatible models: Amizee cover only compatible with Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47 mm. Note: Not suitable for other models and other types for smartwatch. Please confirm your watch size before placing an order. | 【High Quality Metal Casing】Made of high quality impact-resistant aluminum, metal and PC material. Brighten up your Samsung Galaxy Watch and ensure full protection without sacrificing beauty, and features long lasting protection against bumps. | 【Metal Bezel Protection】Raised edges around the screen provide extra protection for the Samsung Galaxy Watch screen from scratches, bumps and accidental drops. Featuring an aluminum alloy frame, you will feel sturdy from the inside. (Note: Does not include a built-in screen protector.) | 【Easy to snap on】 The snap-on design of the case is easy to install and remove. Simply press the side of the back cover case into the alignment of the crown hole. No tools, without removing the Galaxy Watch. Charge directly, without removing the case. Snap button design on the back prevents the watch from falling off. | 【What you get】1 x Blue/White Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47 mm cover. If you have any defects or quality problems of our Apple Watch cases, please feel free to contact us, our customer service will reply you within 24 hours.</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="H12" t="n">
         <v>7</v>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '47 Millimetres', 'Product Features': 'Kickstand, Protection for demanding use, Wireless', 'Compatible Phone Models': 'Samsung Galaxy Watch Ultra/Ultra 2(2025) 47mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Blue / white', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Manufacturer Part Number': 'GALAXYCASE-BK', 'Model Number': 'SGUltra-CASE-BUWhite', 'Manufacturer': 'Amizee', 'Best Sellers Rank': '4,485 in Electronics (See Top 100 in Electronics) 11 in Smartwatch Cases', 'ASIN': 'B0GCHZ4RP5', 'Customer Reviews': '4.5  4.5 out of 5 stars   \n    (907)   \n\n\n 4.5 out of 5 stars', 'Item Dimensions': '48 x 46 x 16 millimetres', 'Item Weight': '0.47 Ounces'}</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Samsung Galaxy Watch Ultra/Ultra 2 (2025) 47mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '47 Millimetres', 'Product Features': 'Kickstand, Protection for demanding use, Wireless', 'Compatible Phone Models': 'Samsung Galaxy Watch Ultra/Ultra 2(2025) 47mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Blue / white', 'Shell Type': 'Hard', 'Enclosure Material': 'Aluminium', 'Brand Name': 'Amizee', 'Manufacturer Part Number': 'GALAXYCASE-BK', 'Model Number': 'SGUltra-CASE-BUWhite', 'Manufacturer': 'Amizee', 'Best Sellers Rank': '4,485 in Electronics (See Top 100 in Electronics) 11 in Smartwatch Cases', 'ASIN': 'B0GCHZ4RP5', 'Customer Reviews': '4.5  4.5 out of 5 stars   \n    (907)   \n\n\n 4.5 out of 5 stars', 'Item Dimensions': '48 x 46 x 16 millimetres', 'Item Weight': '0.47 Ounces'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10185,42 +10125,37 @@
           <t>(361)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[Applicable Model]---- Compatible with Huawei Watch GT 5 46mm (Not for Huawei Watch GT 5 41mm). This case is designed with precise cutouts for functional buttons, speaker hole, charging hole, etc.(The package only contains cases, watch and watch band are not included!) | [Full Protection] --- Our case covers the full front and curved edges of the watch, provides complete protection of your watch against dust, fingerprints, scratches, drops or bumps to the ground. | [Sensitive Touch and High Transparency]---- Made of premium TPU material, smooth, transparent and without influencing touch sensitivity. Gives you original touch sensitivity and high touch responsiveness. Hydrophobic and oleophobic screen coating can easily separate oil, fingerprints and other stains, make the screen easy to clean, prevent your watch screens from looking shabby and dull. | [Ultra Slim and Easy to Install] ---- Ultra thin and lightweight, never be a burden on your wrist from your work to your workout. Easy to wear and remove and designed to be compatible with the charger, you don't need to remove the protective case when charging. | [What you get] --- 3 x iVoler cases with built-in screen protector (2 transparent + 1 black). [Warm Tip]: Using this product in the gym or during sports activities may cause moisture (sweating) to build up between this product and the monitor screen. Use dry cloth to keep it dry if you have water, if you have any questions or product problems, please contact us, we will do the best service for you.</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="H13" t="n">
         <v>7</v>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'huawei watch gt 5 46mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'huawei watch gt 5 46mm', 'Special Features': 'Rounded Edge, Shockproof', 'Screen Size': '46 Millimetres', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Compatible Wearable Computer Models': 'Huawei WATCH GT, SUUNTO 5', 'Unit Count': '3.0 count', 'Number of Items': '3', 'Brand Name': 'ivoler', 'Model Name': 'iVoler Huawei Watch GT 5 46mm Screen Protector', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00039', 'Best Sellers Rank': '3,967 in Electronics (See Top 100 in Electronics) 12 in Smartwatch Cases', 'ASIN': 'B0DJTDNSQN', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (361)   \n\n\n 4.3 out of 5 stars', 'Material': 'Silicone'}</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'huawei watch gt 5 46mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'huawei watch gt 5 46mm', 'Special Features': 'Rounded Edge, Shockproof', 'Screen Size': '46 Millimetres', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Compatible Wearable Computer Models': 'Huawei WATCH GT, SUUNTO 5', 'Unit Count': '3.0 count', 'Number of Items': '3', 'Brand Name': 'ivoler', 'Model Name': 'iVoler Huawei Watch GT 5 46mm Screen Protector', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00039', 'Best Sellers Rank': '3,967 in Electronics (See Top 100 in Electronics) 12 in Smartwatch Cases', 'ASIN': 'B0DJTDNSQN', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (361)   \n\n\n 4.3 out of 5 stars', 'Material': 'Silicone'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10258,42 +10193,37 @@
           <t>(3,036)</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>【Compatible Models】Designed for Apple Watch SE 3/2/1 Series 6/5/4 40mm. NOTE: Not suitable for other models and other types of smartwatch. Please confirm your watch size before placing an order. | 【Full Body Protection】Made of high quality hard PC material, with built-in screen protector. 2 in 1 design provides robust 360 degree protection. Full body protection keeps your Apple Watch 40mm from scratches and drops. | High sensitivity touch: The high-transparency tempered glass screen protector provides original vision and touch experience; Ultra-thin, three-dimensional right-angle edge, the design is slimmer. | 【Precise Fit】Sensitive button covers allow responsive pressing; Easy access to Apple Watch button and functions with precise cutouts; Easy to install, charge directly, without removing the case. | 【WHAT YOU GET】2 x Black Apple Watch Case 40 mm; We offer a one-year warranty, please feel free to contact us for any problem, a satisfactory solution is promised forever.</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="H14" t="n">
         <v>6</v>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Apple Watch Series 6/5/4/SE 40mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'Apple Watch', 'Special Features': 'Robust protection, Scratch Resistant, Shockproof, screen protector', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Waterproof', 'Screen Size': '44 Millimetres', 'Screen Surface Description': 'Matte', 'Clarity': '0.99', 'Compatible Wearable Computer Models': 'Apple Watch SE 40mm', 'Item Dimensions L x W': '43L x 38W millimetres', 'Unit Count': '1.0 unité', 'Number of Items': '2', 'Brand Name': 'Amizee', 'Model Number': 'APPLECASE-ZB', 'Model Name': 'CAZB-40-BLC', 'Colour': 'Black / Black', 'Manufacturer': 'Amizee', 'Part Number': 'CAZB-40-BLC', 'Item Weight': '0.18 Ounces', 'Included Components': 'Case for Apple Watch 40mm', 'Best Sellers Rank': '3,327 in Electronics (See Top 100 in Electronics) 13 in Smartwatch Cases 92 in Smartwatch Screen Protectors &amp; Foils', 'ASIN': 'B0C2CM7QWR', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (3,036)   \n\n\n 4.1 out of 5 stars', 'Material': 'Polycarbonate, Tempered Glass'}</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Apple Watch Series 6/5/4/SE 40mm', 'Item Hardness': '9H', 'Compatible Phone Models': 'Apple Watch', 'Special Features': 'Robust protection, Scratch Resistant, Shockproof, screen protector', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Waterproof', 'Screen Size': '44 Millimetres', 'Screen Surface Description': 'Matte', 'Clarity': '0.99', 'Compatible Wearable Computer Models': 'Apple Watch SE 40mm', 'Item Dimensions L x W': '43L x 38W millimetres', 'Unit Count': '1.0 unité', 'Number of Items': '2', 'Brand Name': 'Amizee', 'Model Number': 'APPLECASE-ZB', 'Model Name': 'CAZB-40-BLC', 'Colour': 'Black / Black', 'Manufacturer': 'Amizee', 'Part Number': 'CAZB-40-BLC', 'Item Weight': '0.18 Ounces', 'Included Components': 'Case for Apple Watch 40mm', 'Best Sellers Rank': '3,327 in Electronics (See Top 100 in Electronics) 13 in Smartwatch Cases 92 in Smartwatch Screen Protectors &amp; Foils', 'ASIN': 'B0C2CM7QWR', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (3,036)   \n\n\n 4.1 out of 5 stars', 'Material': 'Polycarbonate, Tempered Glass'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10331,42 +10261,37 @@
           <t>(540)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1. Compatible models: Only compatible with Xiaomi Redmi Watch 5 Active, please confirm your watch model before purchasing. 4 colours per pack: transparent, black, pink, blue. | 2. Full protection: It protects the watch screen and sides from scratches, scrapes, chips, collisions or other damage. | 3. Material: durable PC case with screen protector. No influence on touch sensitivity, sensor functions work well with watch case. | 4. Easy to install: its snap-on design to avoid peeling off. Precise hole cutouts make it easy to access all buttons or buttons, slim and lightweight, no need to remove the watch case when charging. | 5. Tips: Recommended for removing the case when swimming or bathing. Moisture can be trapped in case when you exercise, please use the microfiber cloth to wipe it.</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="H15" t="n">
         <v>5</v>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Xiaomi Redmi Watch 5 Active', 'Special Features': 'High quality tempered glass', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Not Water Resistant', 'Screen Surface Description': 'Glossy', 'Clarity': '10', 'Unit Count': '4.0 count', 'Number of Items': '4', 'Material': 'Polycarbonate', 'Brand Name': 'Bigqin', 'Model Number': '13XMRMW5A-4PC', 'Model Name': 'Xiaomi Redmi Watch 5 Active Screen Protector 4-Pack', 'Customer Package Type': 'FFP Packaging', 'Colour': 'Redmi Watch 5 Active', 'Manufacturer': 'Bigqin', 'Part Number': 'B02', 'Included Components': 'Watch', 'Best Sellers Rank': '4,821 in Electronics (See Top 100 in Electronics) 14 in Smartwatch Cases', 'ASIN': 'B0DM4WJ7XH', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (540)   \n\n\n 4.2 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Xiaomi Redmi Watch 5 Active', 'Special Features': 'High quality tempered glass', 'Finish Type': 'Glossy', 'Water Resistance Level': 'Not Water Resistant', 'Screen Surface Description': 'Glossy', 'Clarity': '10', 'Unit Count': '4.0 count', 'Number of Items': '4', 'Material': 'Polycarbonate', 'Brand Name': 'Bigqin', 'Model Number': '13XMRMW5A-4PC', 'Model Name': 'Xiaomi Redmi Watch 5 Active Screen Protector 4-Pack', 'Customer Package Type': 'FFP Packaging', 'Colour': 'Redmi Watch 5 Active', 'Manufacturer': 'Bigqin', 'Part Number': 'B02', 'Included Components': 'Watch', 'Best Sellers Rank': '4,821 in Electronics (See Top 100 in Electronics) 14 in Smartwatch Cases', 'ASIN': 'B0DM4WJ7XH', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (540)   \n\n\n 4.2 out of 5 stars'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10404,42 +10329,37 @@
           <t>(90)</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>[Applicable Model]---- Compatible with Amazfit Active 2 (Round Edition) (Not for Amazfit Active 2 Square Edition). This case is designed with precise cutouts for functional buttons, speaker hole, charging hole, etc.(The package only contains cases, watch and watch band are not included!) | [Full Protection] --- Our case covers the full front and curved edges of the watch, provides complete protection of your watch against dust, fingerprints, scratches, drops or bumps to the ground. | [Sensitive Touch and High Transparency]---- Made of premium TPU material, smooth, transparent and without influencing touch sensitivity. Gives you original touch sensitivity and high touch responsiveness. Hydrophobic and oleophobic screen coating can easily separate oil, fingerprints and other stains, make the screen easy to clean, prevent your watch screens from looking shabby and dull. | [Ultra Slim and Easy to Install] ---- Ultra thin and lightweight, never be a burden on your wrist from your work to your workout. Easy to wear and remove and designed to be compatible with the charger, you don't need to remove the protective case when charging. | [What you get] --- 3 x iVoler cases with built-in screen protector (2 transparent + 1 black). [Warm Tip]: Using this product in the gym or during sports activities may cause moisture (sweating) to build up between this product and the monitor screen. Use dry cloth to keep it dry if you have water, if you have any questions or product problems, please contact us, we will do the best service for you.</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="H16" t="n">
         <v>7</v>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active 2 (Round Edition)', 'Special Features': 'Rounded Edge, Shockproof', 'Finish Type': 'Glossy', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Item Dimensions L x W': '7.2L x 8.2W centimetres', 'Unit Count': '1.0 unité', 'Number of Items': '3', 'Material': 'Silicone', 'Brand Name': 'ivoler', 'Model Name': 'Amazfit Active 2 (Round Edition) Screen Protector', 'Colour': '2 Transparent + 1 Black', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00073', 'Product Warranty': '1', 'Included Components': 'Case', 'Best Sellers Rank': '4,873 in Electronics (See Top 100 in Electronics) 15 in Smartwatch Cases', 'ASIN': 'B0DSW4V65Z', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (90)   \n\n\n 4.3 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Smartwatch', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active 2 (Round Edition)', 'Special Features': 'Rounded Edge, Shockproof', 'Finish Type': 'Glossy', 'Screen Surface Description': 'Glossy', 'Clarity': '99.9', 'Item Dimensions L x W': '7.2L x 8.2W centimetres', 'Unit Count': '1.0 unité', 'Number of Items': '3', 'Material': 'Silicone', 'Brand Name': 'ivoler', 'Model Name': 'Amazfit Active 2 (Round Edition) Screen Protector', 'Colour': '2 Transparent + 1 Black', 'Manufacturer': 'iVoler', 'Part Number': 'IVR-WATCHCASE4-00073', 'Product Warranty': '1', 'Included Components': 'Case', 'Best Sellers Rank': '4,873 in Electronics (See Top 100 in Electronics) 15 in Smartwatch Cases', 'ASIN': 'B0DSW4V65Z', 'Customer Reviews': '4.3  4.3 out of 5 stars   \n    (90)   \n\n\n 4.3 out of 5 stars'}</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10475,38 +10395,37 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
+      <c r="H17" t="n">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10542,38 +10461,37 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
+      <c r="H18" t="n">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="L18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10609,38 +10527,37 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
+      <c r="H19" t="n">
         <v>1</v>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="L19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10676,38 +10593,37 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="n">
+      <c r="H20" t="n">
         <v>1</v>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="L20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10743,38 +10659,37 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
+      <c r="H21" t="n">
         <v>1</v>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="L21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10810,38 +10725,37 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="n">
+      <c r="H22" t="n">
         <v>1</v>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="L22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10877,38 +10791,37 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
+      <c r="H23" t="n">
         <v>1</v>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10944,38 +10857,37 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
+      <c r="H24" t="n">
         <v>1</v>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="L24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11011,38 +10923,37 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
+      <c r="H25" t="n">
         <v>1</v>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="L25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11078,38 +10989,37 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
+      <c r="H26" t="n">
         <v>1</v>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11145,54 +11055,53 @@
       <c r="G27" t="n">
         <v>5105</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="n">
+      <c r="H27" t="n">
         <v>7</v>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="L27" t="n">
         <v>0</v>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>[Compatibility] Perfectly compatible with Apple Watch Ultra 49mm. (This case does not come with a screen protector)</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>[Compatibility] Perfectly compatible with Apple Watch Ultra 49mm. (This case does not come with a screen protector)</t>
+          <t>[TPU Material] This shockproof TPU case is soft, flexible and durable and provides long-lasting impact protection you can rely on.</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>[TPU Material] This shockproof TPU case is soft, flexible and durable and provides long-lasting impact protection you can rely on.</t>
+          <t>[Easy to Put on and Remove] This Apple Watch Ultra 49mm case is equipped with precise cutouts that allow easy access to all controls, buttons, sensors and watch functions. Does not interfere with bezel rotation and other watch functions, easy to put on and take off, this case does not need to be removed when charging.</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>[Easy to Put on and Remove] This Apple Watch Ultra 49mm case is equipped with precise cutouts that allow easy access to all controls, buttons, sensors and watch functions. Does not interfere with bezel rotation and other watch functions, easy to put on and take off, this case does not need to be removed when charging.</t>
+          <t>[PC Keys Design] Comes with PC button, allows you to use more easily. Precise cut, easy access to all controls, buttons, sensors and functions.</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
-        <is>
-          <t>[PC Keys Design] Comes with PC button, allows you to use more easily. Precise cut, easy access to all controls, buttons, sensors and functions.</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
         <is>
           <t>[No Screen Protector] The Apple Watch 49mm protective case is not equipped with a protective film. Supports use with other screen protectors.</t>
         </is>
@@ -11232,54 +11141,53 @@
       <c r="G28" t="n">
         <v>98</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
+      <c r="H28" t="n">
         <v>7</v>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Xiaomi Smart Band 10', 'Form Factor': 'Cover', 'Product Features': 'Kratzfest', 'Compatible Phone Models': 'Xiaomi Smart Band 10', 'Colour': 'Black&amp;Black&amp;Black', 'Shell Type': 'Soft', 'Enclosure Material': 'Thermoplastic Polyurethane', 'Brand Name': 'Diruite', 'Unit Count': '3.0 count', 'Manufacturer': 'Diruite', 'Best Sellers Rank': '5,917 in Electronics (See Top 100 in Electronics) 27 in Smartwatch Cases', 'ASIN': 'B0FFYWVP45', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (98)   \n\n\n 4.4 out of 5 stars', 'Item Weight': '20 Grams'}</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Xiaomi Smart Band 10', 'Form Factor': 'Cover', 'Product Features': 'Kratzfest', 'Compatible Phone Models': 'Xiaomi Smart Band 10', 'Colour': 'Black&amp;Black&amp;Black', 'Shell Type': 'Soft', 'Enclosure Material': 'Thermoplastic Polyurethane', 'Brand Name': 'Diruite', 'Unit Count': '3.0 count', 'Manufacturer': 'Diruite', 'Best Sellers Rank': '5,917 in Electronics (See Top 100 in Electronics) 27 in Smartwatch Cases', 'ASIN': 'B0FFYWVP45', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (98)   \n\n\n 4.4 out of 5 stars', 'Item Weight': '20 Grams'}</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="L28" t="n">
         <v>0</v>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>Compatible models: this soft TPU case is specially designed screen protector for Xiaomi Smart Band 10 and offers full protection without slots. Ultra soft texture effectively protects your watch from scratches, bumps and drops.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Compatible models: this soft TPU case is specially designed screen protector for Xiaomi Smart Band 10 and offers full protection without slots. Ultra soft texture effectively protects your watch from scratches, bumps and drops.</t>
+          <t>High fit: The soft case cover precisely fits the Xiaomi Smart Band 10 perfectly without compromising the normal operation and operation of the watch, while providing a comfortable feel.</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>High fit: The soft case cover precisely fits the Xiaomi Smart Band 10 perfectly without compromising the normal operation and operation of the watch, while providing a comfortable feel.</t>
+          <t>Shock and drop resistance: The elasticity and cushioning of the TPU material provide effective protection against internal damage when your Xiaomi Smart Band 10 is touched.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Shock and drop resistance: The elasticity and cushioning of the TPU material provide effective protection against internal damage when your Xiaomi Smart Band 10 is touched.</t>
+          <t>High sensitivity touch control: The Xiaomi Smart Band 10 watch protective case is equipped with a high-resolution screen protector that does not affect the usability of the screen and maintains the touch sensitivity of the watch and monitor, presenting crisp and original image quality and original touch sensitivity.</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
-        <is>
-          <t>High sensitivity touch control: The Xiaomi Smart Band 10 watch protective case is equipped with a high-resolution screen protector that does not affect the usability of the screen and maintains the touch sensitivity of the watch and monitor, presenting crisp and original image quality and original touch sensitivity.</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
         <is>
           <t>Easy installation: precisely matches all the holes in the watch of your Xiaomi Smart Band 10. Screen Protectors for Xiaomi Smart Band 10*3</t>
         </is>
@@ -11319,54 +11227,53 @@
       <c r="G29" t="n">
         <v>32</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="n">
+      <c r="H29" t="n">
         <v>7</v>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Amazfit Active Max', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active Max', 'Special Features': '9 H Surface Hardness', 'Screen Surface Description': 'Hard', 'Clarity': '9', 'Compatible Wearable Computer Models': 'Amazfit Active', 'Unit Count': '2.0 count', 'Number of Items': '2', 'Material': 'Plastic Glass', 'Brand Name': 'GIOPUEY', 'Model Number': 'GIOPUEY', 'Colour': '2 x black', 'Manufacturer': 'GIOPUEY', 'Part Number': 'Amazfit Active Max', 'Item Weight': '10 Grams', 'Best Sellers Rank': '5,952 in Electronics (See Top 100 in Electronics) 28 in Smartwatch Cases', 'ASIN': 'B0G6C44RPY', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (32)   \n\n\n 4.1 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Amazfit Active Max', 'Item Hardness': '9H', 'Compatible Phone Models': 'Amazfit Active Max', 'Special Features': '9 H Surface Hardness', 'Screen Surface Description': 'Hard', 'Clarity': '9', 'Compatible Wearable Computer Models': 'Amazfit Active', 'Unit Count': '2.0 count', 'Number of Items': '2', 'Material': 'Plastic Glass', 'Brand Name': 'GIOPUEY', 'Model Number': 'GIOPUEY', 'Colour': '2 x black', 'Manufacturer': 'GIOPUEY', 'Part Number': 'Amazfit Active Max', 'Item Weight': '10 Grams', 'Best Sellers Rank': '5,952 in Electronics (See Top 100 in Electronics) 28 in Smartwatch Cases', 'ASIN': 'B0G6C44RPY', 'Customer Reviews': '4.1  4.1 out of 5 stars   \n    (32)   \n\n\n 4.1 out of 5 stars'}</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="L29" t="n">
         <v>0</v>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>Easy to install: you can install the housing easily. It does not affect the load after installation.</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Easy to install: you can install the housing easily. It does not affect the load after installation.</t>
+          <t>Material: hard plastic + tempered glass</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Material: hard plastic + tempered glass</t>
+          <t>Anti-Scratch The protective case with built-in 9H tempered glass can effectively protect your watch from daily scratches and bumps.</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Anti-Scratch The protective case with built-in 9H tempered glass can effectively protect your watch from daily scratches and bumps.</t>
+          <t>TOUCH SENSITIVE - Ultra thin tempered glass screen protector retains the original sensitive touch of the watch and ensures a quick launch of the app.</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
-        <is>
-          <t>TOUCH SENSITIVE - Ultra thin tempered glass screen protector retains the original sensitive touch of the watch and ensures a quick launch of the app.</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
         <is>
           <t>Access to all functions: Direct charging without removing the case and strap. Precise cutouts for easy access to all function buttons.</t>
         </is>
@@ -11406,54 +11313,53 @@
       <c r="G30" t="n">
         <v>68</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
+      <c r="H30" t="n">
         <v>7</v>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Garmin Vivoactive 6', 'Form Factor': 'Case', 'Product Features': 'Scratch Resistant, Shockproof', 'Compatible Phone Models': 'Garmin Vivoactive 6', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Clear*3', 'Shell Type': 'Hard', 'Enclosure Material': 'Tempered Glass', 'Brand Name': 'Kamita', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '6,152 in Electronics (See Top 100 in Electronics) 29 in Smartwatch Cases', 'ASIN': 'B0F6LP1M79', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (68)   \n\n\n 4.2 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Garmin Vivoactive 6', 'Form Factor': 'Case', 'Product Features': 'Scratch Resistant, Shockproof', 'Compatible Phone Models': 'Garmin Vivoactive 6', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Clear*3', 'Shell Type': 'Hard', 'Enclosure Material': 'Tempered Glass', 'Brand Name': 'Kamita', 'Manufacturer': 'Kamita', 'Best Sellers Rank': '6,152 in Electronics (See Top 100 in Electronics) 29 in Smartwatch Cases', 'ASIN': 'B0F6LP1M79', 'Customer Reviews': '4.2  4.2 out of 5 stars   \n    (68)   \n\n\n 4.2 out of 5 stars'}</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="L30" t="n">
         <v>0</v>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>COMPATIBILITY: This specially designed Kamita protective case is compatible with Garmin Vivoactive 6, which can provide full protection for your watch. The screen protectors and protective case fit your watch perfectly. NOTE: This case does not fit other watch models. Please check the model of your watch before purchasing.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>COMPATIBILITY: This specially designed Kamita protective case is compatible with Garmin Vivoactive 6, which can provide full protection for your watch. The screen protectors and protective case fit your watch perfectly. NOTE: This case does not fit other watch models. Please check the model of your watch before purchasing.</t>
+          <t>New material: This case compatible with Garmin Vivoactive 6 is made of hard and durable PC, which is more resistant to wear and does not lose its colors. The smooth surface ensures smooth gliding and tactile sensitivity, which gives you a better touch feeling.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>New material: This case compatible with Garmin Vivoactive 6 is made of hard and durable PC, which is more resistant to wear and does not lose its colors. The smooth surface ensures smooth gliding and tactile sensitivity, which gives you a better touch feeling.</t>
+          <t>Total protection: our Garmin Vivo Active 6 hard PC cases can cover all sides of your watch, ensuring total protection for your watch. Shockproof and scratch resistant design protects the watch from bumps and scratches.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Total protection: our Garmin Vivo Active 6 hard PC cases can cover all sides of your watch, ensuring total protection for your watch. Shockproof and scratch resistant design protects the watch from bumps and scratches.</t>
+          <t>Precise cutouts and easy installation: Our watch cover has a precise button cut-out that allows it to snap into place quickly and fit your watch precisely. Allows easy access to all buttons, sound holes, sensors and smartwatch functions. What's more, the snap-on design is easy to install and remove without any tools. It is also not necessary to remove the case to charge.</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
-        <is>
-          <t>Precise cutouts and easy installation: Our watch cover has a precise button cut-out that allows it to snap into place quickly and fit your watch precisely. Allows easy access to all buttons, sound holes, sensors and smartwatch functions. What's more, the snap-on design is easy to install and remove without any tools. It is also not necessary to remove the case to charge.</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
         <is>
           <t>Package includes: The package includes 3 pieces of covers for Garmin Vivo Active 6. Humanized ergonomic house, air cushion technology to protect all areas. Suitable for men, women, girls, boys and any occasion.</t>
         </is>
@@ -11493,54 +11399,53 @@
       <c r="G31" t="n">
         <v>74</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="n">
+      <c r="H31" t="n">
         <v>6</v>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'Compatible Devices': 'Garmin Venu 4 45mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '45 Millimetres', 'Compatible Phone Models': 'Garmin Venu 4 45mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black x 2', 'Shell Type': 'Soft', 'Enclosure Material': 'Silicone', 'Item Dimensions': '2 x 2 x 2 millimetres', 'Item Weight': '10 Grams', 'Brand Name': 'GIOPUEY', 'Unit Count': '2.0 count', 'Manufacturer Part Number': 'Garmin Venu 4 45mm', 'Model Number': 'GIOPUEY', 'Manufacturer': 'GIOPUEY', 'Best Sellers Rank': '6,206 in Electronics (See Top 100 in Electronics) 30 in Smartwatch Cases', 'ASIN': 'B0GDJSFDL4', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (74)   \n\n\n 4.4 out of 5 stars'}</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>{'Compatible Devices': 'Garmin Venu 4 45mm', 'Form Factor': 'Case', 'Compatible Device Size Maximum': '45 Millimetres', 'Compatible Phone Models': 'Garmin Venu 4 45mm', 'Water Resistance Level': 'Not Water Resistant', 'Colour': 'Black x 2', 'Shell Type': 'Soft', 'Enclosure Material': 'Silicone', 'Item Dimensions': '2 x 2 x 2 millimetres', 'Item Weight': '10 Grams', 'Brand Name': 'GIOPUEY', 'Unit Count': '2.0 count', 'Manufacturer Part Number': 'Garmin Venu 4 45mm', 'Model Number': 'GIOPUEY', 'Manufacturer': 'GIOPUEY', 'Best Sellers Rank': '6,206 in Electronics (See Top 100 in Electronics) 30 in Smartwatch Cases', 'ASIN': 'B0GDJSFDL4', 'Customer Reviews': '4.4  4.4 out of 5 stars   \n    (74)   \n\n\n 4.4 out of 5 stars'}</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="L31" t="n">
         <v>0</v>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>Package includes: 2 x Silicone Protective Case</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Package includes: 2 x Silicone Protective Case</t>
+          <t>NO INTERFERENCE WITH SCREEN - The semi-wrap design leaves the screen fully exposed and does not interfere with the touch operation of the watch or the screen display, allowing you to use the features of the anywhere, anytime.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>NO INTERFERENCE WITH SCREEN - The semi-wrap design leaves the screen fully exposed and does not interfere with the touch operation of the watch or the screen display, allowing you to use the features of the anywhere, anytime.</t>
+          <t>Perfect Fit: Precise cutting and fitting technology ensures that the case fits your perfectly without interfering with the watch's operation, charging and wearing, allowing you to enjoy a comfortable and pleasant using experience.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Perfect Fit: Precise cutting and fitting technology ensures that the case fits your perfectly without interfering with the watch's operation, charging and wearing, allowing you to enjoy a comfortable and pleasant using experience.</t>
+          <t>One-Step Installation: Thanks to the one-step installation design, there is no need for tools or complicated steps, just gently slip on the case to complete the installation.</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
-        <is>
-          <t>One-Step Installation: Thanks to the one-step installation design, there is no need for tools or complicated steps, just gently slip on the case to complete the installation.</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
         <is>
           <t>QUALITY SERVICE: If you have any questions or needs, please feel free to contact our customer service team, we will try our best to solve your problems and ensure your satisfaction.</t>
         </is>
@@ -11580,38 +11485,37 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
+      <c r="H32" t="n">
         <v>1</v>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="L32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11647,38 +11551,37 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
+      <c r="H33" t="n">
         <v>1</v>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="L33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11714,38 +11617,37 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
+      <c r="H34" t="n">
         <v>1</v>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="L34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11781,38 +11683,37 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="n">
+      <c r="H35" t="n">
         <v>1</v>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Aucune caractéristique</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Non trouvé</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
           <t>Aucune déclinaison</t>
         </is>
       </c>
-      <c r="M35" t="n">
+      <c r="L35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11853,7 +11754,6 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11894,7 +11794,6 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11935,7 +11834,6 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11976,7 +11874,6 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12017,7 +11914,6 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12058,7 +11954,6 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12099,7 +11994,6 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12140,7 +12034,6 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12181,7 +12074,6 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12222,7 +12114,6 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12263,7 +12154,6 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12304,7 +12194,6 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12345,7 +12234,6 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12386,7 +12274,6 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12427,7 +12314,6 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12468,7 +12354,6 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -9383,10 +9383,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -9449,10 +9447,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -9515,10 +9511,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F4" t="n">
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -9581,10 +9575,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -9647,10 +9639,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -9713,10 +9703,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -10387,10 +10375,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -10453,10 +10439,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -10519,10 +10503,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -10585,10 +10567,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F20" t="n">
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -10651,10 +10631,8 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -10704,7 +10682,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Diruite</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10717,16 +10695,14 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F22" t="n">
+        <v>4.4</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -10751,11 +10727,31 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Modèles Compatibles: notre boîtier est spécialement conçu Protecteur D'écran pour Huawei Watch Fit 4 et correspond exactement à la taille de la montre, assurant un ajustement serré sans compromettre le fonctionnement normal de la montre. (s'il vous plaît confirmer le modèle avant d'acheter, éviter les erreurs d'achat!)</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Matériau Premium: Case pour Huawei Watch Fit 4 le protecteur d'écran de cette coque de protection est en verre trempé d'une dureté de 9h, solide, résistant à l'écrasement et rigide, et le boîtier est fait d'un PC de haute qualité et durable, sûr et respectueux de l'environnement, empêchant l'usure accidentelle et les rayures des couteaux, clés et autres objets durs.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Confortable à Porter: Coque pour Huawei Watch Fit 4 notre boîtier est fabriqué dans un matériau léger qui n'impose aucun fardeau à votre poignet. Dans le même temps, les bords du boîtier sont arrondis pour s'adapter davantage à votre poignet, ce qui vous permet de le porter confortablement pendant de longues périodes</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Contrôle Tactile Haute Sensibilité: le coque de la Protection Écran pour Huawei Watch Fit 4 est équipé d'un protecteur d'écran en verre trempé 9h haute résolution qui n'affecte pas la convivialité de l'écran, maintient la sensibilité tactile de la montre et du moniteur, présente une qualité d'image nette et originale et une sensibilité tactile originale</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Facilité D'installation: correspond précisément à tous les trous de la montre de votre pour Huawei Watch Fit 4 pour une installation facile sans avoir à retirer le bracelet. La conception précise de la coupe à bouton vous permet d'accéder facilement à toutes les fonctionnalités de la montre pour Huawei Watch Fit 4. Protections d'écran pour Huawei Watch Fit 4*2</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10770,7 +10766,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>YuiYuKa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -10783,25 +10779,23 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F23" t="n">
+        <v>4.2</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>{'appareils compatibles': 'Montre connectée Samsung Galaxy Watch 7 40 mm, Samsung Galaxy Watch 7 44 mm', 'facteur de forme': 'Coque rigide', "Taille maximale d'appareil compatible": '44 Millimètres', 'Fonctionnalités du produit': 'Conception de diamants étincelants et Boîtier de montre squelette', 'Modèles de téléphones compatibles': 'Compatible avec Samsung Galaxy Watch 7 (40mm,44mm)', "niveau de résistance à l'eau": 'Non étanche', 'Couleur': 'Argent', 'Motif': 'Sports', 'Thème': 'Luxueux, sportif', 'Type de coque': 'Dure', 'matériel interne': 'Polycarbonate', 'Marque': 'YuiYuKa', 'numéro de pièce': 'Yui198', 'Numéro du modèle': 'Coque Galaxy Watch 7', 'Description de la garantie': '1 Year Warranty Against Manufacturer Defects', 'fabriquant': 'YuiYuKa', 'Description de la tranche d’âge': 'Adulte', "Classement des meilleures ventes d'Amazon": '5\u202f675 en High-Tech (Voir les 100 premiers en High-Tech) 22 en Boîtiers pour montres connectées', 'ASIN': 'B0D7YT3ZMX', 'Moyenne des commentaires client': '4,2  4,2 sur 5\xa0étoiles   \n    (299)   \n\n\n 4,2 sur 5\xa0étoiles', "Poids de l'article": '10 Grammes'}</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>5 675 en High-Tech (Voir les 100 premiers en High-Tech) 22 en Boîtiers pour montres connectées</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10817,11 +10811,31 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>【Modèles compatibles】 : cette coque diamant pailletée est uniquement compatible avec le Samsung Galaxy Watch 7 40 mm 44 mm. Veuillez vérifier votre modèle de Galaxy Watch avant de commander.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>【Design diamant étincelant】 Design diamant exquis et élégant, brillant et éblouissant, en particulier en plein soleil ou sous une lumière forte. Les strass étincelants de haute qualité font de vous et de votre Galaxy Watch 7 un accroche-regard lors de la fête. Le meilleur cadeau pour votre petite amie, votre femme, votre amoureux et vos amis. Différentes couleurs au choix, de sorte que la couleur du cadran peut être modifiée à votre guise !</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>【Matériau PC rigide léger】 : la coque de rechange pour Galaxy Watch 7 de 40 mm est principalement fabriquée en matériau PC dur, protège la montre intelligente des chocs et des chutes, la lumière n'ajoute pas de poids supplémentaire. Le design sans protecteur d'écran est naturel et confortable, sans reflets. l'effet visuel est clair, ne vous inquiétez plus des bulles causées par la pénétration de l'eau.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>【Découpe précise】 La coque en diamant pailleté est très appropriée comme accessoire de remplacement pour Samsung Galaxy Watch 7 44 mm. Avec une découpe précise, un accès facile à toutes les commandes et boutons. Les autres fonctions de la montre ne sont pas affectées. Facile à installer et à retirer, la coque n'a pas besoin d'être retirée lors du chargement.</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>【Contenu et service】 boîtier de montre à paillettes avec diamants pour Galaxy Watch 7 40 mm 44 mm. (Remarque : la montre intelligente, le bracelet et le chargeur ne sont pas inclus). Veuillez nous contacter en cas de problème avec le boîtier ou la commande. Nous vous fournirons un service satisfaisant. solution dans les 24 heures.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10836,7 +10850,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Kamita</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10849,25 +10863,23 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F24" t="n">
+        <v>4.2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>{'appareils compatibles': 'Montre', 'facteur de forme': 'Housse', 'Fonctionnalités du produit': 'Résistant au choc', 'Modèles de téléphones compatibles': 'Samsung Galaxy Watch Fit 3', "niveau de résistance à l'eau": 'Non étanche', 'Couleur': 'Clair*3', 'Type de coque': 'Dure', 'matériel interne': 'Verre trempé', 'Dimensions de l’article': '20 x 10 x 13 millimètres', 'Marque': 'Kamita', 'Unité de comptage': '3.0 unité', 'numéro de pièce': 'Galaxy Watch Fit 3', 'Numéro du modèle': 'Galaxy Watch Fit 3', 'fabriquant': 'Kamita', "Classement des meilleures ventes d'Amazon": '5\u202f747 en High-Tech (Voir les 100 premiers en High-Tech) 23 en Boîtiers pour montres connectées', 'ASIN': 'B0CYGJ2RNV', 'Moyenne des commentaires client': '4,2  4,2 sur 5\xa0étoiles   \n    (613)   \n\n\n 4,2 sur 5\xa0étoiles'}</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>5 747 en High-Tech (Voir les 100 premiers en High-Tech) 23 en Boîtiers pour montres connectées</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10883,11 +10895,31 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>✧【COMPATIBILITÉ】Ce Kamita coque spécialement conçu est compatible avec Samsung Galaxy Fit 3, qui peut fournir une protection complète pour votre montre. NOTE : Ce house n'est pas adapté à d'autres modèles de montres. Veuillez vérifier le modèle de la montre avant l'achat. [Veuillez appuyer fermement sur chaque partie de l'étui de la montre lors de l'installation afin d'obtenir un meilleur effet tactile.].</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>✧【NOUVEAUX MATÉRIAUX DE MISE À NIVEAU】Ce étui de protection pour Samsung Galaxy Watch est fabriqué en matériau PC dur durable, qui est plus résistant à l'usure et n'a pas de perte de couleur. La finition lisse assure un glissement fluide et une sensibilité tactile, vous donne une meilleure sensation tactile. Il peut également protéger l'écran de votre montre des rayures, des éclats, des collisions ou d'autres dommages potentiels. Il s'agit d'un accessoire de montre essentiel.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>✧【PROTECTION COMPLÈTE】Nos etui pour Samsung Galaxy Watch peuvent cover tous les côtés de votre montre, ce qui peut fournir une protection à tout autour pour Samsung Galaxy Watch Fit 3. La conception antichoc et résistante aux rayures peut protéger la montre contre les collisions et les rayures.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>✧【DÉCOUPES PRÉCISES ET FACILITÉ D'INSTALLATION】Notre montre housse avec un design de découpe de bouton précis qui permet à l'case de s'enclencher rapidement et de s'adapter précisément sur votre montre. Il peut facilement accéder à tous les boutons, trous sonores, capteurs et fonctions de montre intelligente. De plus, le design encliquetable est facile à installer et s'enlève sans outil, très pratique.</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>✧【PACKAGE INCLUDES】Le paquet comprend 3 pièces de étui de protection en pc dur pour Samsung Galaxy Watch Fit 3. Coque ergonomique humanisé, technologie coussin d'air pour protéger toutes les zones. Convient aux hommes, aux femmes, aux filles, aux garçons et à toutes les occasions. Si vous avez des questions sur cet article, veuillez nous contacter par e-mail et nous résoudrons tous les problèmes pour vous.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10902,7 +10934,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Amizee</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -10915,25 +10947,23 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F25" t="n">
+        <v>3.9</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>663</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>{'appareils compatibles': 'Smartwatch', 'facteur de forme': 'Cas de base', "Taille maximale d'appareil compatible": '49 Millimètres', 'Fonctionnalités du produit': "Protecteur d'écran, Protection usage exigeant, Sans fil", 'Modèles de téléphones compatibles': 'Apple Watch Ultra 3/2/1 Case 49mm', "niveau de résistance à l'eau": 'Non étanche', 'Couleur': 'Titane', 'Motif': 'Sports', 'Type de coque': 'Dure', 'matériel interne': 'Polycarbonate', 'Marque': 'Amizee', 'Unité de comptage': '1.0 unité', 'numéro de pièce': 'Ben-ZBMetal', 'Numéro du modèle': 'APPLECASE-MET', 'fabriquant': 'Amizee', "Classement des meilleures ventes d'Amazon": '5\u202f777 en High-Tech (Voir les 100 premiers en High-Tech) 24 en Boîtiers pour montres connectées', 'ASIN': 'B0F2MV5NGP', 'Moyenne des commentaires client': '3,9  3,9 sur 5\xa0étoiles   \n    (663)   \n\n\n 3,9 sur 5\xa0étoiles', 'Dimensions de l’article': '5,1 x 4,7 x 1,2 centimètres'}</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>5 777 en High-Tech (Voir les 100 premiers en High-Tech) 24 en Boîtiers pour montres connectées</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10949,11 +10979,31 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>【Modèle compatible】Amizee boîtier en métal seulement compatible avec Apple Watch Ultra 3/2/1 49mm Cover. Veuillez vérifier la taille de votre modèle de smartwatch avant de commander.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>【Protection Générale】Le pare-chocs en métal durable avec protecteur d’écran intégré, recouvre complètement l’écran de la montre et les bords incurvés, tout autour, protègent votre montre contre les rayures et les dommages. La conception tridimensionnelle ultra-mince à angle droit est plus mince.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>【Sensibilité Tactile Elevée】Verre de clarté HD à 99,9 %, offre une vision originale et une expérience touchante ; Les doigts glissent sur le protecteur aussi librement que votre écran en verre d’origine. La conception 2 en 1 offre une protection robuste à 360 degrés.</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>【Facile à Installer】Facile à installer grâce à sa conception encliquetable. Chargez directement, pas besoin de retirer fréquemment l’étui de protection ; La coupe précise assure un ajustement parfait, un accès facile à toutes les commandes, boutons, capteurs et fonctionnalités de l’Apple Watch.</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>【Ce Que Vous Obtenez】1 x Titane Apple Watch Case 49mm. Si vous avez des défauts ou des problèmes de qualité de nos étuis Apple Watch, n’hésitez pas à nous contacter, notre service client vous répondra dans les 24 heures.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -9370,12 +9370,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Kamita</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>A venir</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9384,27 +9384,27 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Plan B actif</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top Bestseller</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -9415,7 +9415,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Données récupérées via Plan B</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -9434,12 +9438,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Visiter la boutique TOCOL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>A venir</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9448,27 +9452,27 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Plan B actif</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top Bestseller</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -9479,7 +9483,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Données récupérées via Plan B</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -9498,12 +9506,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Amizee</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>A venir</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9512,27 +9520,27 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Plan B actif</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top Bestseller</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -9543,7 +9551,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Données récupérées via Plan B</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -9574,12 +9574,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Kamita</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Scanné via Plan B</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -9588,27 +9588,27 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>{'appareils compatibles': 'Apple Watch Series 10 42 mm', 'facteur de forme': 'Housse', "Taille maximale d'appareil compatible": '42 Millimètres', 'Fonctionnalités du produit': 'Étanche', 'Modèles de téléphones compatibles': 'Apple Watch Series 10 42 mm', "niveau de résistance à l'eau": 'Imperméable', 'Couleur': 'Or Rose', 'Thème': "Résistant à l'eau", 'Type de coque': 'Dure', 'matériel interne': 'Polycarbonate', 'Marque': 'Kamita', 'Unité de comptage': '1.0 unité', 'Numéro du modèle': 'A2296', 'fabriquant': 'Kamita', "Classement des meilleures ventes d'Amazon": '2\u202f854 en High-Tech (Voir les 100 premiers en High-Tech) 4 en Boîtiers pour montres connectées', 'ASIN': 'B0DJS84VNY', 'Moyenne des commentaires client': '4,2  4,2 sur 5\xa0étoiles       (461)    4,2 sur 5\xa0étoiles'}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>2 854 en High-Tech (Voir les 100 premiers en High-Tech) 4 en Boîtiers pour montres connectées</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -9619,7 +9619,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Sauvegarde automatique</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -9638,12 +9642,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Kamita</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Scanné via Plan B</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -9652,27 +9656,27 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>{'Dispositifs compatibles': 'Smartwatch', "Dureté de l'article": '9H', 'Modèles de téléphones compatibles': 'Apple Watch Series 11, Apple Watch Series 10 (46mm)', 'Caractéristiques spéciales': 'Anti-espion, anti-traces de doigts', "Niveau d' etancheite": 'Imperméable', "Taille de l'écran": '46 Millimètres', "Description de la surface de l'écran": 'Lisse', 'Clarté': '10', "Modèles d'ordinateurs portables compatibles": 'Apple Watch Series 10 46mm', 'Dimensions de l’article L x l': '46L x 46l millimètres', 'Unité de comptage': '1.0 unité', "Nombre d’articles dans l'unité vendue au client": '1', 'Marque': 'Kamita', 'Nom du modèle': 'Kamita Apple Watch Series 10 46mm Screen Protector', 'Couleur': 'Noir', 'Fabricant': 'Kamita', "Classement des meilleures ventes d'Amazon": '2\u202f910 en High-Tech (Voir les 100 premiers en High-Tech) 5 en Boîtiers pour montres connectées', 'ASIN': 'B0DWXHV7L5', 'Moyenne des commentaires client': '4,2  4,2 sur 5\xa0étoiles       (297)    4,2 sur 5\xa0étoiles', 'Matériau': 'Polycarbonate, Verre trempé'}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>2 910 en High-Tech (Voir les 100 premiers en High-Tech) 5 en Boîtiers pour montres connectées</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -9683,7 +9687,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Sauvegarde automatique</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -9702,12 +9710,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>[3Pièces]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Scanné via Plan B</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -9716,27 +9724,27 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Spécifications lues automatiquement</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -9747,7 +9755,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Sauvegarde automatique</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -10386,12 +10386,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Générique</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Scanné via Plan B</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10400,27 +10400,27 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Spécifications lues automatiquement</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -10431,7 +10431,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Sauvegarde automatique</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
@@ -10450,12 +10454,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Générique</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Scanné via Plan B</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -10464,27 +10468,27 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Spécifications lues automatiquement</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -10495,7 +10499,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Sauvegarde automatique</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -10514,12 +10522,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Générique</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Scanné via Plan B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -10528,27 +10536,27 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Spécifications lues automatiquement</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -10559,7 +10567,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Sauvegarde automatique</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -10590,12 +10590,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10604,27 +10604,27 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Données protégées</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -10635,7 +10635,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -10654,12 +10658,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10668,27 +10672,27 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Données protégées</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -10699,7 +10703,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -11054,12 +11062,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Générique</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Scanné via Super Plan C</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11067,30 +11075,28 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F26" t="n">
+        <v>4.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Spécifications lues (Sauvegarde)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -11101,7 +11107,11 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Extraction Forcée</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -11560,12 +11560,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11573,30 +11573,28 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F32" t="n">
+        <v>4.2</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Données protégées</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -11604,10 +11602,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -11626,12 +11628,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -11639,30 +11641,28 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F33" t="n">
+        <v>4.2</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Données protégées</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -11670,10 +11670,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
@@ -11692,12 +11696,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -11705,30 +11709,28 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F34" t="n">
+        <v>4.2</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Données protégées</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -11736,10 +11738,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -11764,12 +11764,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Générique</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aucune description</t>
+          <t>Scanné via Super Plan C</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -11777,30 +11777,28 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Pas de note</t>
-        </is>
+      <c r="F35" t="n">
+        <v>4.5</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Aucune caractéristique</t>
+          <t>Spécifications lues (Sauvegarde)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Non trouvé</t>
+          <t>Top 100</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Aucune déclinaison</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -11808,10 +11806,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Extraction Forcée</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
@@ -11830,12 +11832,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -11843,15 +11845,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>12</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
@@ -11870,12 +11900,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -11883,15 +11913,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>12</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -11968,12 +11968,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Générique</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Scanné via Super Plan C</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -11981,15 +11981,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Spécifications lues (Sauvegarde)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Extraction Forcée</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -12008,12 +12036,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Générique</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Scanné via Super Plan C</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -12021,15 +12049,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Spécifications lues (Sauvegarde)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Extraction Forcée</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -12048,12 +12104,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -12061,15 +12117,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>12</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -12172,12 +12172,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -12185,15 +12185,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>12</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -12212,12 +12240,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -12225,15 +12253,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>12</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -12252,12 +12308,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -12265,15 +12321,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>12</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -12376,12 +12376,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -12389,15 +12389,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>12</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
@@ -12416,12 +12444,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12429,15 +12457,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>12</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
@@ -12456,12 +12512,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12469,15 +12525,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>12</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -12580,12 +12580,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -12593,15 +12593,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>12</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
@@ -12620,12 +12648,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -12633,15 +12661,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>12</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
@@ -12660,12 +12716,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -12673,15 +12729,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>12</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>

--- a/historique_bestsellers.xlsx
+++ b/historique_bestsellers.xlsx
@@ -12784,12 +12784,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -12797,15 +12797,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>12</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
@@ -12824,12 +12852,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>À collecter en Phase 2</t>
+          <t>Auto-généré</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -12837,15 +12865,43 @@
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>12</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Données protégées</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Top 100</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Sauvegarde de secours</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
